--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -39,6 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
@@ -63,31 +117,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,19 +315,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
+        <fgColor rgb="FFB32230"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,36 +333,786 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -171,12 +1125,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -195,25 +1167,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,19 +1191,283 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,31 +1479,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,36 +1509,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -333,1441 +1611,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF52B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF52B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5018,7 +5018,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5033,40 +5033,40 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="10">
         <v>7.05</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="3">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="11">
         <v>-12.87</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="12">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>-27.1</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="1">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="5">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="6">
         <v>-29.13</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="13">
         <v>-38.48</v>
       </c>
-      <c r="T2" s="9">
+      <c r="T2" s="8">
         <v>-22.49</v>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       <c r="C3" t="str">
         <v>601086</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 1112.14万</v>
       </c>
       <c r="E3">
@@ -5095,40 +5095,40 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="20">
         <v>0</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="24">
         <v>10.07</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="16">
         <v>21.01</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="26">
         <v>33.16</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="17">
         <v>46.53</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="18">
         <v>61.11</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="21">
         <v>51.39</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="22">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="19">
         <v>83.16</v>
       </c>
       <c r="R3" s="14">
         <v>101.56</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="25">
         <v>121.7</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="23">
         <v>56.25</v>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       <c r="C4" t="str">
         <v>601798</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 691.01万</v>
       </c>
       <c r="E4">
@@ -5157,40 +5157,40 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="37">
         <v>0</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="30">
         <v>2.79</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="27">
         <v>-5.03</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="28">
         <v>-4.19</v>
       </c>
       <c r="M4" s="33">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="38">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="39">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="31">
         <v>-4.89</v>
       </c>
       <c r="Q4" s="34">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="35">
         <v>-2.09</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="36">
         <v>2.09</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="32">
         <v>26.68</v>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5219,22 +5219,22 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="44">
         <v>15.75</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="51">
         <v>7.62</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="45">
         <v>10.11</v>
       </c>
       <c r="L5" s="52">
         <v>21.1</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="40">
         <v>20.88</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="47">
         <v>8.79</v>
       </c>
       <c r="O5" s="48">
@@ -5243,13 +5243,13 @@
       <c r="P5" s="41">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="49">
         <v>44.84</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="42">
         <v>53.85</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="50">
         <v>38.46</v>
       </c>
       <c r="T5" s="43">
@@ -5266,7 +5266,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5281,37 +5281,37 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="65">
         <v>1.99</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="53">
         <v>-8.15</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="56">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="54">
         <v>-12.52</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="60">
         <v>-11.93</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="61">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="55">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="57">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="58">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="62">
         <v>-6.96</v>
       </c>
       <c r="T6" s="59">
@@ -5328,7 +5328,7 @@
       <c r="C7" t="str">
         <v>603280</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="67" t="str">
         <v>净买: 1485.07万</v>
       </c>
       <c r="E7">
@@ -5343,40 +5343,40 @@
       <c r="H7">
         <v>1.66</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="77">
         <v>8.18</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="72">
         <v>4.83</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="69">
         <v>0.58</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="70">
         <v>1.75</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="78">
         <v>2.46</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="73">
         <v>1.01</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="74">
         <v>0.47</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="66">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="71">
         <v>2.53</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="75">
         <v>0.19</v>
       </c>
       <c r="S7" s="76">
         <v>0.62</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="68">
         <v>35.66</v>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5405,40 +5405,40 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="80">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="86">
         <v>-6.15</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="89">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="90">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="87">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="81">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="82">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="83">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="85">
         <v>-6.51</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="88">
         <v>-6.11</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="84">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="90">
+      <c r="T8" s="91">
         <v>26.58</v>
       </c>
     </row>
@@ -5467,40 +5467,40 @@
       <c r="H9">
         <v>4.88</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="100">
         <v>4.9</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="97">
         <v>3.27</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="101">
         <v>0.21</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="99">
         <v>2.76</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="98">
         <v>-7.5</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="93">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="94">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="102">
         <v>-9.17</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="103">
         <v>-9.05</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="104">
         <v>-9.89</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S9" s="95">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="95">
+      <c r="T9" s="92">
         <v>-23.71</v>
       </c>
     </row>
@@ -5529,40 +5529,40 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="108">
         <v>0</v>
       </c>
       <c r="J10" s="112">
         <v>-10</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="109">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="114">
+      <c r="L10" s="117">
         <v>-15</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="105">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="113">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="106">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="110">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="114">
         <v>-18.29</v>
       </c>
-      <c r="R10" s="109">
+      <c r="R10" s="107">
         <v>-18.03</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="115">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="116">
         <v>-20.53</v>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       <c r="C11" t="str">
         <v>600620</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="121" t="str">
         <v>净卖: -737.07万</v>
       </c>
       <c r="E11">
@@ -5591,40 +5591,40 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="118">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="124">
         <v>-5.51</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="119">
         <v>-6.38</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="125">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="127">
+      <c r="M11" s="126">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="128">
+      <c r="N11" s="123">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="123">
+      <c r="O11" s="122">
         <v>-9.13</v>
       </c>
-      <c r="P11" s="121">
+      <c r="P11" s="120">
         <v>-10</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="127">
         <v>-9.71</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="128">
         <v>-8.84</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="129">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="118">
+      <c r="T11" s="130">
         <v>-12.46</v>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       <c r="C12" t="str">
         <v>603966</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 1229.54万</v>
       </c>
       <c r="E12">
@@ -5653,40 +5653,40 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="141">
         <v>0</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="142">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="132">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="143">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="133">
         <v>-11.82</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="135">
         <v>-15.09</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="136">
         <v>-16.1</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="131">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="137">
         <v>-16.17</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="138">
         <v>-14.77</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="139">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="133">
+      <c r="T12" s="134">
         <v>8.79</v>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="146" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5715,40 +5715,40 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="149">
         <v>13.73</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="147">
         <v>2.32</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="148">
         <v>0.87</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="150">
         <v>5.22</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="155">
         <v>-1.26</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="145">
         <v>-7.06</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="151">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="152">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="156">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="153">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="144">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="152">
+      <c r="T13" s="154">
         <v>-18.47</v>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="157" t="str">
+      <c r="D14" s="161" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5777,40 +5777,40 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="162">
         <v>1.04</v>
       </c>
       <c r="J14" s="163">
         <v>0.19</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="159">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="157">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="160">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="164">
         <v>-9.74</v>
       </c>
-      <c r="O14" s="165">
+      <c r="O14" s="158">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="168">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="165">
         <v>4.35</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="166">
         <v>14.74</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="167">
         <v>11.15</v>
       </c>
-      <c r="T14" s="162">
+      <c r="T14" s="169">
         <v>92.16</v>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5839,40 +5839,40 @@
       <c r="H15">
         <v>-2.72</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="173">
         <v>7.54</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="178">
         <v>-3.18</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="170">
         <v>-0.19</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="174">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="175">
         <v>0.32</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="179">
         <v>1.56</v>
       </c>
-      <c r="O15" s="182">
+      <c r="O15" s="180">
         <v>11.7</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="171">
         <v>15.01</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="181">
         <v>12.02</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="182">
         <v>3.18</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="172">
         <v>0.06</v>
       </c>
-      <c r="T15" s="178">
+      <c r="T15" s="176">
         <v>1.56</v>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -5901,40 +5901,40 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="184">
         <v>0</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="185">
         <v>6.11</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="193">
         <v>16.72</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="186">
         <v>28.39</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="183">
         <v>29.42</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="187">
         <v>16.48</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="189">
         <v>28.13</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="188">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="194">
         <v>26.42</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="190">
         <v>18.15</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="195">
         <v>24.82</v>
       </c>
-      <c r="T16" s="189">
+      <c r="T16" s="191">
         <v>414.83</v>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="200" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -5963,40 +5963,40 @@
       <c r="H17">
         <v>-0.61</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="201">
         <v>-1.22</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="202">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="197">
         <v>-16.16</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="203">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="204">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="205">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="207">
         <v>-30.18</v>
       </c>
-      <c r="P17" s="207">
+      <c r="P17" s="208">
         <v>-27.13</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="196">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="198">
         <v>-25.3</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="206">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="204">
+      <c r="T17" s="199">
         <v>-26.52</v>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6025,40 +6025,40 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="211">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="217">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="218">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="212">
         <v>-15.5</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="213">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="214">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="219">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="209">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="215">
+      <c r="Q18" s="210">
         <v>-2.95</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="220">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="221">
         <v>-2.58</v>
       </c>
-      <c r="T18" s="221">
+      <c r="T18" s="215">
         <v>-11.07</v>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="223" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6093,34 +6093,34 @@
       <c r="J19" s="230">
         <v>0.83</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="233">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="234">
         <v>-7.94</v>
       </c>
       <c r="M19" s="231">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="232">
+      <c r="N19" s="225">
         <v>-11.11</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="222">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="233">
+      <c r="P19" s="226">
         <v>-7.5</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="227">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="228">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="226">
+      <c r="S19" s="229">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="228">
+      <c r="T19" s="232">
         <v>-10.22</v>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="239" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6149,40 +6149,40 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="240">
         <v>0</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="235">
         <v>9.85</v>
       </c>
       <c r="K20" s="244">
         <v>20.8</v>
       </c>
-      <c r="L20" s="240">
+      <c r="L20" s="245">
         <v>25.55</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="246">
         <v>14.23</v>
       </c>
-      <c r="N20" s="246">
+      <c r="N20" s="241">
         <v>2.92</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="236">
         <v>-7.3</v>
       </c>
       <c r="P20" s="237">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="238">
+      <c r="Q20" s="242">
         <v>-12.77</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="238">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="245">
+      <c r="S20" s="247">
         <v>-12.41</v>
       </c>
-      <c r="T20" s="247">
+      <c r="T20" s="243">
         <v>-51.09</v>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="256" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6211,40 +6211,40 @@
       <c r="H21">
         <v>10.01</v>
       </c>
-      <c r="I21" s="252">
+      <c r="I21" s="254">
         <v>0</v>
       </c>
-      <c r="J21" s="258">
+      <c r="J21" s="251">
         <v>10</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="257">
         <v>21</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="258">
         <v>8.91</v>
       </c>
       <c r="M21" s="259">
         <v>-1.99</v>
       </c>
-      <c r="N21" s="254">
+      <c r="N21" s="252">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="249">
         <v>-3.41</v>
       </c>
-      <c r="P21" s="255">
+      <c r="P21" s="250">
         <v>-10.42</v>
       </c>
       <c r="Q21" s="260">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="253">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="248">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="248">
+      <c r="T21" s="255">
         <v>-18.04</v>
       </c>
     </row>
@@ -6353,37 +6353,37 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="266">
+      <c r="I24" s="268">
         <v>38.1</v>
       </c>
-      <c r="J24" s="272">
+      <c r="J24" s="276">
         <v>61.9</v>
       </c>
-      <c r="K24" s="273">
+      <c r="K24" s="277">
         <v>42.86</v>
       </c>
-      <c r="L24" s="269">
+      <c r="L24" s="271">
         <v>40</v>
       </c>
-      <c r="M24" s="276">
+      <c r="M24" s="272">
         <v>30</v>
       </c>
-      <c r="N24" s="274">
+      <c r="N24" s="273">
         <v>30</v>
       </c>
-      <c r="O24" s="267">
+      <c r="O24" s="269">
         <v>25</v>
       </c>
       <c r="P24" s="270">
         <v>30</v>
       </c>
-      <c r="Q24" s="277">
+      <c r="Q24" s="274">
         <v>30</v>
       </c>
-      <c r="R24" s="268">
+      <c r="R24" s="266">
         <v>30</v>
       </c>
-      <c r="S24" s="271">
+      <c r="S24" s="267">
         <v>35</v>
       </c>
       <c r="T24" s="275">
@@ -6401,40 +6401,40 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="284">
+      <c r="I25" s="282">
         <v>2.3</v>
       </c>
-      <c r="J25" s="287">
+      <c r="J25" s="283">
         <v>0.89</v>
       </c>
-      <c r="K25" s="288">
+      <c r="K25" s="280">
         <v>0.11</v>
       </c>
-      <c r="L25" s="282">
+      <c r="L25" s="286">
         <v>-0.39</v>
       </c>
-      <c r="M25" s="283">
+      <c r="M25" s="287">
         <v>-1.6</v>
       </c>
-      <c r="N25" s="285">
+      <c r="N25" s="288">
         <v>-3.91</v>
       </c>
-      <c r="O25" s="289">
+      <c r="O25" s="284">
         <v>-3.03</v>
       </c>
-      <c r="P25" s="286">
+      <c r="P25" s="285">
         <v>-1</v>
       </c>
-      <c r="Q25" s="278">
+      <c r="Q25" s="289">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="280">
+      <c r="R25" s="278">
         <v>0.57</v>
       </c>
-      <c r="S25" s="281">
+      <c r="S25" s="279">
         <v>1.47</v>
       </c>
-      <c r="T25" s="279">
+      <c r="T25" s="281">
         <v>22.43</v>
       </c>
     </row>

--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -51,6 +51,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF61BE76"/>
         <bgColor/>
       </patternFill>
@@ -69,24 +99,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -105,24 +117,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -135,6 +141,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -153,12 +165,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -195,13 +327,343 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF27A644"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,13 +675,223 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,25 +903,277 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,18 +1185,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -291,31 +1203,517 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF52B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,1447 +1725,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF5C5C9"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF52B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5018,7 +5018,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5033,40 +5033,40 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>7.05</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="8">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="9">
         <v>-12.87</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="3">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="10">
         <v>-27.1</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="5">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="13">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="6">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="1">
         <v>-29.13</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="2">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="4">
         <v>-38.48</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="7">
         <v>-22.49</v>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       <c r="C3" t="str">
         <v>601086</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 1112.14万</v>
       </c>
       <c r="E3">
@@ -5095,40 +5095,40 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="18">
         <v>0</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="21">
         <v>10.07</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="19">
         <v>21.01</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="22">
         <v>33.16</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="26">
         <v>46.53</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="14">
         <v>61.11</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="15">
         <v>51.39</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="20">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="23">
         <v>83.16</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="24">
         <v>101.56</v>
       </c>
       <c r="S3" s="25">
         <v>121.7</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="17">
         <v>56.25</v>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       <c r="C4" t="str">
         <v>601798</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 691.01万</v>
       </c>
       <c r="E4">
@@ -5157,40 +5157,40 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="36">
         <v>0</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="32">
         <v>2.79</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="38">
         <v>-5.03</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="39">
         <v>-4.19</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="27">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="33">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="28">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="34">
         <v>-4.89</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="29">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="37">
         <v>-2.09</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="30">
         <v>2.09</v>
       </c>
-      <c r="T4" s="32">
+      <c r="T4" s="35">
         <v>26.68</v>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5219,40 +5219,40 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="48">
         <v>15.75</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="42">
         <v>7.62</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="43">
         <v>10.11</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="50">
         <v>21.1</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="51">
         <v>20.88</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="49">
         <v>8.79</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="44">
         <v>19.71</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="45">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="46">
         <v>44.84</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="47">
         <v>53.85</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="52">
         <v>38.46</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="40">
         <v>-3.3</v>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="55" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5281,40 +5281,40 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="58">
         <v>0</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="59">
         <v>1.99</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="54">
         <v>-8.15</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="60">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="64">
         <v>-12.52</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="65">
         <v>-11.93</v>
       </c>
       <c r="O6" s="61">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="56">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="62">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="57">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="63">
         <v>-6.96</v>
       </c>
-      <c r="T6" s="59">
+      <c r="T6" s="53">
         <v>13.32</v>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       <c r="C7" t="str">
         <v>603280</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="70" t="str">
         <v>净买: 1485.07万</v>
       </c>
       <c r="E7">
@@ -5343,40 +5343,40 @@
       <c r="H7">
         <v>1.66</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="71">
         <v>8.18</v>
       </c>
       <c r="J7" s="72">
         <v>4.83</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="68">
         <v>0.58</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="73">
         <v>1.75</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="74">
         <v>2.46</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="75">
         <v>1.01</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="76">
         <v>0.47</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="77">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="66">
         <v>2.53</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="78">
         <v>0.19</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="67">
         <v>0.62</v>
       </c>
-      <c r="T7" s="68">
+      <c r="T7" s="69">
         <v>35.66</v>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="80" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5405,40 +5405,40 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="81">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="85">
         <v>-6.15</v>
       </c>
       <c r="K8" s="89">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="82">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="90">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="91">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="83">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="87">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="84">
         <v>-6.51</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="79">
         <v>-6.11</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="86">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="88">
         <v>26.58</v>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       <c r="C9" t="str">
         <v>600148</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -235.34万</v>
       </c>
       <c r="E9">
@@ -5467,40 +5467,40 @@
       <c r="H9">
         <v>4.88</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="93">
         <v>4.9</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="96">
         <v>3.27</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="97">
         <v>0.21</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="98">
         <v>2.76</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="94">
         <v>-7.5</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="104">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="95">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="92">
         <v>-9.17</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="99">
         <v>-9.05</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="100">
         <v>-9.89</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="101">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="92">
+      <c r="T9" s="102">
         <v>-23.71</v>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       <c r="C10" t="str">
         <v>600620</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="106" t="str">
         <v>净买: 848.83万</v>
       </c>
       <c r="E10">
@@ -5529,40 +5529,40 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="113">
         <v>0</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="107">
         <v>-10</v>
       </c>
-      <c r="K10" s="109">
+      <c r="K10" s="116">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="110">
         <v>-15</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="117">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="114">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="111">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="115">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="112">
         <v>-18.29</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="108">
         <v>-18.03</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="105">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="116">
+      <c r="T10" s="109">
         <v>-20.53</v>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       <c r="C11" t="str">
         <v>600620</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="118" t="str">
         <v>净卖: -737.07万</v>
       </c>
       <c r="E11">
@@ -5591,40 +5591,40 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="127">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="123">
         <v>-5.51</v>
       </c>
       <c r="K11" s="119">
         <v>-6.38</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="128">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="129">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="130">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="124">
         <v>-9.13</v>
       </c>
       <c r="P11" s="120">
         <v>-10</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="121">
         <v>-9.71</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="122">
         <v>-8.84</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="126">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="130">
+      <c r="T11" s="125">
         <v>-12.46</v>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       <c r="C12" t="str">
         <v>603966</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="142" t="str">
         <v>净买: 1229.54万</v>
       </c>
       <c r="E12">
@@ -5653,19 +5653,19 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="137">
         <v>0</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="143">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="134">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="140">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="138">
         <v>-11.82</v>
       </c>
       <c r="N12" s="135">
@@ -5674,19 +5674,19 @@
       <c r="O12" s="136">
         <v>-16.1</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="141">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="131">
         <v>-16.17</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="132">
         <v>-14.77</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="133">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="134">
+      <c r="T12" s="139">
         <v>8.79</v>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="147" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5715,40 +5715,40 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="144">
         <v>13.73</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="148">
         <v>2.32</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="153">
         <v>0.87</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="149">
         <v>5.22</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="150">
         <v>-1.26</v>
       </c>
       <c r="N13" s="145">
         <v>-7.06</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="152">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="154">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="156">
+      <c r="Q13" s="146">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="155">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="151">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="154">
+      <c r="T13" s="156">
         <v>-18.47</v>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="166" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5777,40 +5777,40 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="163">
         <v>1.04</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="167">
         <v>0.19</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="164">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="157">
+      <c r="L14" s="168">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="169">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="159">
         <v>-9.74</v>
       </c>
-      <c r="O14" s="158">
+      <c r="O14" s="160">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="161">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="162">
         <v>4.35</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="157">
         <v>14.74</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="158">
         <v>11.15</v>
       </c>
-      <c r="T14" s="169">
+      <c r="T14" s="165">
         <v>92.16</v>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5842,37 +5842,37 @@
       <c r="I15" s="173">
         <v>7.54</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="182">
         <v>-3.18</v>
       </c>
       <c r="K15" s="170">
         <v>-0.19</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="175">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="176">
         <v>0.32</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="171">
         <v>1.56</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="172">
         <v>11.7</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="177">
         <v>15.01</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="179">
         <v>12.02</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="178">
         <v>3.18</v>
       </c>
-      <c r="S15" s="172">
+      <c r="S15" s="174">
         <v>0.06</v>
       </c>
-      <c r="T15" s="176">
+      <c r="T15" s="180">
         <v>1.56</v>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -5901,40 +5901,40 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="184">
+      <c r="I16" s="191">
         <v>0</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="184">
         <v>6.11</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="192">
         <v>16.72</v>
       </c>
       <c r="L16" s="186">
         <v>28.39</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="187">
         <v>29.42</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="193">
         <v>16.48</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="188">
         <v>28.13</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="194">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="194">
+      <c r="Q16" s="195">
         <v>26.42</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="183">
         <v>18.15</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="189">
         <v>24.82</v>
       </c>
-      <c r="T16" s="191">
+      <c r="T16" s="185">
         <v>414.83</v>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="207" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -5969,34 +5969,34 @@
       <c r="J17" s="202">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="198">
         <v>-16.16</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="206">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="199">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="208">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="200">
         <v>-30.18</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="203">
         <v>-27.13</v>
       </c>
       <c r="Q17" s="196">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="197">
         <v>-25.3</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="204">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="199">
+      <c r="T17" s="205">
         <v>-26.52</v>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="215" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6025,40 +6025,40 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="214">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="217">
+      <c r="J18" s="210">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="216">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="212">
+      <c r="L18" s="211">
         <v>-15.5</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="217">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="218">
         <v>-11.81</v>
       </c>
       <c r="O18" s="219">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="209">
+      <c r="P18" s="220">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="221">
         <v>-2.95</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="209">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="212">
         <v>-2.58</v>
       </c>
-      <c r="T18" s="215">
+      <c r="T18" s="213">
         <v>-11.07</v>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6087,40 +6087,40 @@
       <c r="H19">
         <v>-7.17</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="229">
         <v>-3.06</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="225">
         <v>0.83</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="222">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="230">
         <v>-7.94</v>
       </c>
-      <c r="M19" s="231">
+      <c r="M19" s="223">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="231">
         <v>-11.11</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="226">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="232">
         <v>-7.5</v>
       </c>
-      <c r="Q19" s="227">
+      <c r="Q19" s="233">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="228">
+      <c r="R19" s="234">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="229">
+      <c r="S19" s="224">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="232">
+      <c r="T19" s="227">
         <v>-10.22</v>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="239" t="str">
+      <c r="D20" s="240" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6149,40 +6149,40 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="240">
+      <c r="I20" s="241">
         <v>0</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="242">
         <v>9.85</v>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="245">
         <v>20.8</v>
       </c>
-      <c r="L20" s="245">
+      <c r="L20" s="243">
         <v>25.55</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="236">
         <v>14.23</v>
       </c>
-      <c r="N20" s="241">
+      <c r="N20" s="237">
         <v>2.92</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="246">
         <v>-7.3</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="247">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="235">
         <v>-12.77</v>
       </c>
       <c r="R20" s="238">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="244">
         <v>-12.41</v>
       </c>
-      <c r="T20" s="243">
+      <c r="T20" s="239">
         <v>-51.09</v>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="256" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6214,37 +6214,37 @@
       <c r="I21" s="254">
         <v>0</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="255">
         <v>10</v>
       </c>
-      <c r="K21" s="257">
+      <c r="K21" s="256">
         <v>21</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="251">
         <v>8.91</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="257">
         <v>-1.99</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="258">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="249">
+      <c r="O21" s="260">
         <v>-3.41</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="248">
         <v>-10.42</v>
       </c>
-      <c r="Q21" s="260">
+      <c r="Q21" s="252">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="249">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="250">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="255">
+      <c r="T21" s="259">
         <v>-18.04</v>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       <c r="C22" t="str">
         <v>603950</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="261" t="str">
         <v>净买: 6471.95万</v>
       </c>
       <c r="E22">
@@ -6273,13 +6273,13 @@
       <c r="H22">
         <v>5.99</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="262">
         <v>3.78</v>
       </c>
-      <c r="J22" s="265">
+      <c r="J22" s="263">
         <v>6.92</v>
       </c>
-      <c r="K22" s="261">
+      <c r="K22" s="264">
         <v>13.09</v>
       </c>
       <c r="L22" t="str"/>
@@ -6290,7 +6290,7 @@
       <c r="Q22" t="str"/>
       <c r="R22" t="str"/>
       <c r="S22" t="str"/>
-      <c r="T22" s="262">
+      <c r="T22" s="265">
         <v>13.09</v>
       </c>
     </row>
@@ -6353,40 +6353,40 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="268">
+      <c r="I24" s="277">
         <v>38.1</v>
       </c>
-      <c r="J24" s="276">
+      <c r="J24" s="270">
         <v>61.9</v>
       </c>
-      <c r="K24" s="277">
+      <c r="K24" s="272">
         <v>42.86</v>
       </c>
-      <c r="L24" s="271">
+      <c r="L24" s="274">
         <v>40</v>
       </c>
-      <c r="M24" s="272">
+      <c r="M24" s="275">
         <v>30</v>
       </c>
       <c r="N24" s="273">
         <v>30</v>
       </c>
-      <c r="O24" s="269">
+      <c r="O24" s="266">
         <v>25</v>
       </c>
-      <c r="P24" s="270">
+      <c r="P24" s="271">
         <v>30</v>
       </c>
-      <c r="Q24" s="274">
+      <c r="Q24" s="267">
         <v>30</v>
       </c>
-      <c r="R24" s="266">
+      <c r="R24" s="268">
         <v>30</v>
       </c>
-      <c r="S24" s="267">
+      <c r="S24" s="276">
         <v>35</v>
       </c>
-      <c r="T24" s="275">
+      <c r="T24" s="269">
         <v>47.62</v>
       </c>
     </row>
@@ -6401,37 +6401,37 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="282">
+      <c r="I25" s="285">
         <v>2.3</v>
       </c>
-      <c r="J25" s="283">
+      <c r="J25" s="286">
         <v>0.89</v>
       </c>
-      <c r="K25" s="280">
+      <c r="K25" s="287">
         <v>0.11</v>
       </c>
-      <c r="L25" s="286">
+      <c r="L25" s="283">
         <v>-0.39</v>
       </c>
-      <c r="M25" s="287">
+      <c r="M25" s="278">
         <v>-1.6</v>
       </c>
-      <c r="N25" s="288">
+      <c r="N25" s="279">
         <v>-3.91</v>
       </c>
-      <c r="O25" s="284">
+      <c r="O25" s="280">
         <v>-3.03</v>
       </c>
-      <c r="P25" s="285">
+      <c r="P25" s="288">
         <v>-1</v>
       </c>
-      <c r="Q25" s="289">
+      <c r="Q25" s="284">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="278">
+      <c r="R25" s="282">
         <v>0.57</v>
       </c>
-      <c r="S25" s="279">
+      <c r="S25" s="289">
         <v>1.47</v>
       </c>
       <c r="T25" s="281">

--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="291">
+  <fills count="292">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -57,13 +57,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,19 +105,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFCD2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,42 +309,726 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -171,12 +1041,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -189,31 +1101,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,19 +1191,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,43 +1203,253 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,37 +1461,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,1363 +1713,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1707,72 +1749,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196E2F"/>
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="290">
+  <borders count="291">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3807,7 +3820,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="291">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4674,6 +4687,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="289" fillId="290" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="290" fillId="291" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5018,7 +5034,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5033,41 +5049,41 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="6">
         <v>7.05</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="9">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5">
         <v>-12.87</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="7">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="13">
         <v>-27.1</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="10">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="1">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="11">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="12">
         <v>-29.13</v>
       </c>
       <c r="R2" s="2">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <v>-38.48</v>
       </c>
-      <c r="T2" s="7">
-        <v>-22.49</v>
+      <c r="T2" s="8">
+        <v>-21.54</v>
       </c>
     </row>
     <row r="3">
@@ -5080,7 +5096,7 @@
       <c r="C3" t="str">
         <v>601086</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 1112.14万</v>
       </c>
       <c r="E3">
@@ -5095,41 +5111,41 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="25">
         <v>0</v>
       </c>
       <c r="J3" s="21">
         <v>10.07</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="22">
         <v>21.01</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="14">
         <v>33.16</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="17">
         <v>46.53</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="18">
         <v>61.11</v>
       </c>
       <c r="O3" s="15">
         <v>51.39</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="16">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="19">
         <v>83.16</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="26">
         <v>101.56</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="23">
         <v>121.7</v>
       </c>
-      <c r="T3" s="17">
-        <v>56.25</v>
+      <c r="T3" s="20">
+        <v>52.26</v>
       </c>
     </row>
     <row r="4">
@@ -5142,7 +5158,7 @@
       <c r="C4" t="str">
         <v>601798</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 691.01万</v>
       </c>
       <c r="E4">
@@ -5157,10 +5173,10 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="34">
         <v>0</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="29">
         <v>2.79</v>
       </c>
       <c r="K4" s="38">
@@ -5169,29 +5185,29 @@
       <c r="L4" s="39">
         <v>-4.19</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="30">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="35">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="27">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="31">
         <v>-4.89</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="33">
         <v>-2.09</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="28">
         <v>2.09</v>
       </c>
-      <c r="T4" s="35">
-        <v>26.68</v>
+      <c r="T4" s="37">
+        <v>28.91</v>
       </c>
     </row>
     <row r="5">
@@ -5204,7 +5220,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5219,41 +5235,41 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="49">
         <v>15.75</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="40">
         <v>7.62</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="50">
         <v>10.11</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="45">
         <v>21.1</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="41">
         <v>20.88</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="46">
         <v>8.79</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="47">
         <v>19.71</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="51">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="48">
         <v>44.84</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="42">
         <v>53.85</v>
       </c>
       <c r="S5" s="52">
         <v>38.46</v>
       </c>
-      <c r="T5" s="40">
-        <v>-3.3</v>
+      <c r="T5" s="44">
+        <v>6.37</v>
       </c>
     </row>
     <row r="6">
@@ -5266,7 +5282,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="58" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5281,41 +5297,41 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="59">
         <v>0</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="53">
         <v>1.99</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="60">
         <v>-8.15</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="54">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="56">
         <v>-12.52</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="61">
         <v>-11.93</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="57">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="62">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="55">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="63">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="64">
         <v>-6.96</v>
       </c>
-      <c r="T6" s="53">
-        <v>13.32</v>
+      <c r="T6" s="65">
+        <v>14.71</v>
       </c>
     </row>
     <row r="7">
@@ -5346,38 +5362,38 @@
       <c r="I7" s="71">
         <v>8.18</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="66">
         <v>4.83</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="74">
         <v>0.58</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="77">
         <v>1.75</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="75">
         <v>2.46</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="72">
         <v>1.01</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="67">
         <v>0.47</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="73">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="68">
         <v>2.53</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="76">
         <v>0.19</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="69">
         <v>0.62</v>
       </c>
-      <c r="T7" s="69">
-        <v>35.66</v>
+      <c r="T7" s="78">
+        <v>36.28</v>
       </c>
     </row>
     <row r="8">
@@ -5390,7 +5406,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="86" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5405,41 +5421,41 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="90">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="87">
         <v>-6.15</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="84">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="80">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="81">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="82">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="91">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="88">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="89">
         <v>-6.51</v>
       </c>
       <c r="R8" s="79">
         <v>-6.11</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="83">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="88">
-        <v>26.58</v>
+      <c r="T8" s="85">
+        <v>27.16</v>
       </c>
     </row>
     <row r="9">
@@ -5452,7 +5468,7 @@
       <c r="C9" t="str">
         <v>600148</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -235.34万</v>
       </c>
       <c r="E9">
@@ -5470,38 +5486,38 @@
       <c r="I9" s="93">
         <v>4.9</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="94">
         <v>3.27</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="104">
         <v>0.21</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="92">
         <v>2.76</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="95">
         <v>-7.5</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="98">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="101">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="96">
         <v>-9.17</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="102">
         <v>-9.05</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="97">
         <v>-9.89</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="103">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="102">
-        <v>-23.71</v>
+      <c r="T9" s="99">
+        <v>-23.63</v>
       </c>
     </row>
     <row r="10">
@@ -5514,7 +5530,7 @@
       <c r="C10" t="str">
         <v>600620</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 848.83万</v>
       </c>
       <c r="E10">
@@ -5529,41 +5545,41 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="115">
         <v>0</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="116">
         <v>-10</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="108">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="117">
         <v>-15</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="112">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="109">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="113">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="110">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="111">
         <v>-18.29</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="114">
         <v>-18.03</v>
       </c>
       <c r="S10" s="105">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="109">
-        <v>-20.53</v>
+      <c r="T10" s="106">
+        <v>-19.87</v>
       </c>
     </row>
     <row r="11">
@@ -5591,41 +5607,41 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="123">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="119">
         <v>-5.51</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="124">
         <v>-6.38</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="129">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="125">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="130">
+      <c r="N11" s="120">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="124">
+      <c r="O11" s="126">
         <v>-9.13</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="130">
         <v>-10</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="127">
         <v>-9.71</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="121">
         <v>-8.84</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="128">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="125">
-        <v>-12.46</v>
+      <c r="T11" s="122">
+        <v>-11.74</v>
       </c>
     </row>
     <row r="12">
@@ -5638,7 +5654,7 @@
       <c r="C12" t="str">
         <v>603966</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 1229.54万</v>
       </c>
       <c r="E12">
@@ -5653,41 +5669,41 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="136">
         <v>0</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="137">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="132">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="140">
+      <c r="L12" s="141">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="138">
+      <c r="M12" s="133">
         <v>-11.82</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="134">
         <v>-15.09</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="143">
         <v>-16.1</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="142">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="138">
         <v>-16.17</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="139">
         <v>-14.77</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="131">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="139">
-        <v>8.79</v>
+      <c r="T12" s="140">
+        <v>9.8</v>
       </c>
     </row>
     <row r="13">
@@ -5700,7 +5716,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="152" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5715,41 +5731,41 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="154">
         <v>13.73</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="150">
         <v>2.32</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="144">
         <v>0.87</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="145">
         <v>5.22</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="146">
         <v>-1.26</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="153">
         <v>-7.06</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="147">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="151">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="146">
+      <c r="Q13" s="155">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="155">
+      <c r="R13" s="148">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="156">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="156">
-        <v>-18.47</v>
+      <c r="T13" s="149">
+        <v>-18.18</v>
       </c>
     </row>
     <row r="14">
@@ -5762,7 +5778,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="166" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5777,41 +5793,41 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="168">
         <v>1.04</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="164">
         <v>0.19</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="169">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="162">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="163">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="157">
         <v>-9.74</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="159">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="165">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="160">
         <v>4.35</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="161">
         <v>14.74</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="166">
         <v>11.15</v>
       </c>
-      <c r="T14" s="165">
-        <v>92.16</v>
+      <c r="T14" s="167">
+        <v>98.77</v>
       </c>
     </row>
     <row r="15">
@@ -5824,7 +5840,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5839,41 +5855,41 @@
       <c r="H15">
         <v>-2.72</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="179">
         <v>7.54</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="178">
         <v>-3.18</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="180">
         <v>-0.19</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="170">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="171">
         <v>0.32</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="181">
         <v>1.56</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="176">
         <v>11.7</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="172">
         <v>15.01</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="177">
         <v>12.02</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="173">
         <v>3.18</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="182">
         <v>0.06</v>
       </c>
-      <c r="T15" s="180">
-        <v>1.56</v>
+      <c r="T15" s="174">
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -5886,7 +5902,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -5901,41 +5917,41 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="193">
         <v>0</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="188">
         <v>6.11</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="185">
         <v>16.72</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="189">
         <v>28.39</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="194">
         <v>29.42</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="186">
         <v>16.48</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="190">
         <v>28.13</v>
       </c>
-      <c r="P16" s="194">
+      <c r="P16" s="195">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="191">
         <v>26.42</v>
       </c>
       <c r="R16" s="183">
         <v>18.15</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="184">
         <v>24.82</v>
       </c>
-      <c r="T16" s="185">
-        <v>414.83</v>
+      <c r="T16" s="187">
+        <v>441.72</v>
       </c>
     </row>
     <row r="17">
@@ -5948,7 +5964,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="203" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -5963,40 +5979,40 @@
       <c r="H17">
         <v>-0.61</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="208">
         <v>-1.22</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="201">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="196">
         <v>-16.16</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="197">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="202">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="198">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="204">
         <v>-30.18</v>
       </c>
-      <c r="P17" s="203">
+      <c r="P17" s="199">
         <v>-27.13</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="200">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="205">
         <v>-25.3</v>
       </c>
-      <c r="S17" s="204">
+      <c r="S17" s="206">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="205">
+      <c r="T17" s="207">
         <v>-26.52</v>
       </c>
     </row>
@@ -6010,7 +6026,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="215" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6025,37 +6041,37 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="220">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="214">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="217">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="210">
         <v>-15.5</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="211">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="212">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="218">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="221">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="209">
         <v>-2.95</v>
       </c>
-      <c r="R18" s="209">
+      <c r="R18" s="215">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="219">
         <v>-2.58</v>
       </c>
       <c r="T18" s="213">
@@ -6072,7 +6088,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="232" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6087,41 +6103,41 @@
       <c r="H19">
         <v>-7.17</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="223">
         <v>-3.06</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="224">
         <v>0.83</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="234">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="233">
         <v>-7.94</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="225">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="228">
         <v>-11.11</v>
       </c>
       <c r="O19" s="226">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="222">
         <v>-7.5</v>
       </c>
-      <c r="Q19" s="233">
+      <c r="Q19" s="229">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="227">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="224">
+      <c r="S19" s="230">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="227">
-        <v>-10.22</v>
+      <c r="T19" s="231">
+        <v>-10.17</v>
       </c>
     </row>
     <row r="20">
@@ -6134,7 +6150,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="242" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6149,41 +6165,41 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="235">
         <v>0</v>
       </c>
-      <c r="J20" s="242">
+      <c r="J20" s="236">
         <v>9.85</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="243">
         <v>20.8</v>
       </c>
-      <c r="L20" s="243">
+      <c r="L20" s="240">
         <v>25.55</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="237">
         <v>14.23</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="244">
         <v>2.92</v>
       </c>
-      <c r="O20" s="246">
+      <c r="O20" s="238">
         <v>-7.3</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="246">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="239">
         <v>-12.77</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="241">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="247">
         <v>-12.41</v>
       </c>
-      <c r="T20" s="239">
-        <v>-51.09</v>
+      <c r="T20" s="245">
+        <v>-50.73</v>
       </c>
     </row>
     <row r="21">
@@ -6196,7 +6212,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="252" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6211,41 +6227,41 @@
       <c r="H21">
         <v>10.01</v>
       </c>
-      <c r="I21" s="254">
+      <c r="I21" s="253">
         <v>0</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="260">
         <v>10</v>
       </c>
-      <c r="K21" s="256">
+      <c r="K21" s="249">
         <v>21</v>
       </c>
-      <c r="L21" s="251">
+      <c r="L21" s="257">
         <v>8.91</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="254">
         <v>-1.99</v>
       </c>
       <c r="N21" s="258">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="260">
+      <c r="O21" s="255">
         <v>-3.41</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="250">
         <v>-10.42</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="259">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="248">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="251">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="259">
-        <v>-18.04</v>
+      <c r="T21" s="256">
+        <v>-15.21</v>
       </c>
     </row>
     <row r="22">
@@ -6282,7 +6298,9 @@
       <c r="K22" s="264">
         <v>13.09</v>
       </c>
-      <c r="L22" t="str"/>
+      <c r="L22" s="265">
+        <v>6.1</v>
+      </c>
       <c r="M22" t="str"/>
       <c r="N22" t="str"/>
       <c r="O22" t="str"/>
@@ -6290,8 +6308,8 @@
       <c r="Q22" t="str"/>
       <c r="R22" t="str"/>
       <c r="S22" t="str"/>
-      <c r="T22" s="265">
-        <v>13.09</v>
+      <c r="T22" s="266">
+        <v>6.1</v>
       </c>
     </row>
     <row r="23">
@@ -6315,7 +6333,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M23">
         <v>20</v>
@@ -6353,41 +6371,41 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="277">
+      <c r="I24" s="267">
         <v>38.1</v>
       </c>
-      <c r="J24" s="270">
+      <c r="J24" s="278">
         <v>61.9</v>
       </c>
-      <c r="K24" s="272">
+      <c r="K24" s="271">
         <v>42.86</v>
       </c>
-      <c r="L24" s="274">
-        <v>40</v>
-      </c>
-      <c r="M24" s="275">
+      <c r="L24" s="268">
+        <v>42.86</v>
+      </c>
+      <c r="M24" s="272">
         <v>30</v>
       </c>
       <c r="N24" s="273">
         <v>30</v>
       </c>
-      <c r="O24" s="266">
+      <c r="O24" s="274">
         <v>25</v>
       </c>
-      <c r="P24" s="271">
+      <c r="P24" s="269">
         <v>30</v>
       </c>
-      <c r="Q24" s="267">
+      <c r="Q24" s="275">
         <v>30</v>
       </c>
-      <c r="R24" s="268">
+      <c r="R24" s="276">
         <v>30</v>
       </c>
-      <c r="S24" s="276">
+      <c r="S24" s="277">
         <v>35</v>
       </c>
-      <c r="T24" s="269">
-        <v>47.62</v>
+      <c r="T24" s="270">
+        <v>52.38</v>
       </c>
     </row>
     <row r="25">
@@ -6401,41 +6419,41 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="285">
+      <c r="I25" s="287">
         <v>2.3</v>
       </c>
-      <c r="J25" s="286">
+      <c r="J25" s="288">
         <v>0.89</v>
       </c>
-      <c r="K25" s="287">
+      <c r="K25" s="282">
         <v>0.11</v>
       </c>
-      <c r="L25" s="283">
-        <v>-0.39</v>
-      </c>
-      <c r="M25" s="278">
+      <c r="L25" s="289">
+        <v>-0.09</v>
+      </c>
+      <c r="M25" s="285">
         <v>-1.6</v>
       </c>
-      <c r="N25" s="279">
+      <c r="N25" s="290">
         <v>-3.91</v>
       </c>
-      <c r="O25" s="280">
+      <c r="O25" s="283">
         <v>-3.03</v>
       </c>
-      <c r="P25" s="288">
+      <c r="P25" s="280">
         <v>-1</v>
       </c>
-      <c r="Q25" s="284">
+      <c r="Q25" s="281">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="282">
+      <c r="R25" s="286">
         <v>0.57</v>
       </c>
-      <c r="S25" s="289">
+      <c r="S25" s="284">
         <v>1.47</v>
       </c>
-      <c r="T25" s="281">
-        <v>22.43</v>
+      <c r="T25" s="279">
+        <v>24.51</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="292">
+  <fills count="293">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -45,6 +45,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -69,54 +117,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -135,6 +135,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -177,25 +183,907 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,31 +1095,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,42 +1149,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -291,13 +1167,295 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,7 +1467,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,1393 +1485,289 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1723,62 +1783,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF52B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="291">
+  <borders count="292">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3820,7 +3833,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="292">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4690,6 +4703,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="290" fillId="291" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="291" fillId="292" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5034,7 +5050,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5049,41 +5065,41 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="2">
         <v>7.05</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="6">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="7">
         <v>-12.87</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="11">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="8">
         <v>-27.1</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="10">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="3">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="4">
         <v>-29.13</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="13">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="1">
         <v>-38.48</v>
       </c>
-      <c r="T2" s="8">
-        <v>-21.54</v>
+      <c r="T2" s="5">
+        <v>-21.95</v>
       </c>
     </row>
     <row r="3">
@@ -5096,7 +5112,7 @@
       <c r="C3" t="str">
         <v>601086</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 1112.14万</v>
       </c>
       <c r="E3">
@@ -5111,37 +5127,37 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="14">
         <v>10.07</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="18">
         <v>21.01</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="15">
         <v>33.16</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="21">
         <v>46.53</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="19">
         <v>61.11</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="22">
         <v>51.39</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="23">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="16">
         <v>83.16</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="24">
         <v>101.56</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="25">
         <v>121.7</v>
       </c>
       <c r="T3" s="20">
@@ -5158,7 +5174,7 @@
       <c r="C4" t="str">
         <v>601798</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 691.01万</v>
       </c>
       <c r="E4">
@@ -5173,41 +5189,41 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="30">
         <v>0</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="34">
         <v>2.79</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="39">
         <v>-5.03</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="31">
         <v>-4.19</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="27">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="36">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="28">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="35">
         <v>-4.89</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="32">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="29">
         <v>-2.09</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="37">
         <v>2.09</v>
       </c>
-      <c r="T4" s="37">
-        <v>28.91</v>
+      <c r="T4" s="33">
+        <v>28.07</v>
       </c>
     </row>
     <row r="5">
@@ -5220,7 +5236,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5235,41 +5251,41 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="52">
         <v>15.75</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="48">
         <v>7.62</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="49">
         <v>10.11</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="40">
         <v>21.1</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="50">
         <v>20.88</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="44">
         <v>8.79</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="41">
         <v>19.71</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="42">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="45">
         <v>44.84</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="43">
         <v>53.85</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="46">
         <v>38.46</v>
       </c>
-      <c r="T5" s="44">
-        <v>6.37</v>
+      <c r="T5" s="47">
+        <v>4.47</v>
       </c>
     </row>
     <row r="6">
@@ -5282,7 +5298,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5297,41 +5313,41 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="65">
         <v>0</v>
       </c>
       <c r="J6" s="53">
         <v>1.99</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="54">
         <v>-8.15</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="59">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="55">
         <v>-12.52</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="60">
         <v>-11.93</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="61">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="56">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="62">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="57">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="63">
         <v>-6.96</v>
       </c>
-      <c r="T6" s="65">
-        <v>14.71</v>
+      <c r="T6" s="58">
+        <v>12.33</v>
       </c>
     </row>
     <row r="7">
@@ -5344,7 +5360,7 @@
       <c r="C7" t="str">
         <v>603280</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 1485.07万</v>
       </c>
       <c r="E7">
@@ -5359,41 +5375,41 @@
       <c r="H7">
         <v>1.66</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="66">
         <v>8.18</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="76">
         <v>4.83</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="67">
         <v>0.58</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="68">
         <v>1.75</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="77">
         <v>2.46</v>
       </c>
       <c r="N7" s="72">
         <v>1.01</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="70">
         <v>0.47</v>
       </c>
       <c r="P7" s="73">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="78">
         <v>2.53</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="69">
         <v>0.19</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="71">
         <v>0.62</v>
       </c>
-      <c r="T7" s="78">
-        <v>36.28</v>
+      <c r="T7" s="74">
+        <v>36.13</v>
       </c>
     </row>
     <row r="8">
@@ -5406,7 +5422,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5421,41 +5437,41 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="80">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="82">
         <v>-6.15</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="83">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="88">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="84">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="85">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8" s="89">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="79">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="81">
         <v>-6.51</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="86">
         <v>-6.11</v>
       </c>
-      <c r="S8" s="83">
+      <c r="S8" s="90">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="85">
-        <v>27.16</v>
+      <c r="T8" s="91">
+        <v>27.02</v>
       </c>
     </row>
     <row r="9">
@@ -5468,7 +5484,7 @@
       <c r="C9" t="str">
         <v>600148</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -235.34万</v>
       </c>
       <c r="E9">
@@ -5483,41 +5499,41 @@
       <c r="H9">
         <v>4.88</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="98">
         <v>4.9</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="96">
         <v>3.27</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="99">
         <v>0.21</v>
       </c>
       <c r="L9" s="92">
         <v>2.76</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="102">
         <v>-7.5</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="97">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="100">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="103">
         <v>-9.17</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="104">
         <v>-9.05</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="93">
         <v>-9.89</v>
       </c>
-      <c r="S9" s="103">
+      <c r="S9" s="94">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="99">
-        <v>-23.63</v>
+      <c r="T9" s="101">
+        <v>-23.71</v>
       </c>
     </row>
     <row r="10">
@@ -5530,7 +5546,7 @@
       <c r="C10" t="str">
         <v>600620</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 848.83万</v>
       </c>
       <c r="E10">
@@ -5545,41 +5561,41 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="111">
         <v>0</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="112">
         <v>-10</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="113">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="108">
         <v>-15</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="114">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="115">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="105">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="106">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="107">
         <v>-18.29</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="116">
         <v>-18.03</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="117">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="106">
-        <v>-19.87</v>
+      <c r="T10" s="109">
+        <v>-19.61</v>
       </c>
     </row>
     <row r="11">
@@ -5592,7 +5608,7 @@
       <c r="C11" t="str">
         <v>600620</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="128" t="str">
         <v>净卖: -737.07万</v>
       </c>
       <c r="E11">
@@ -5607,41 +5623,41 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="123">
+      <c r="I11" s="125">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="121">
         <v>-5.51</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="119">
         <v>-6.38</v>
       </c>
       <c r="L11" s="129">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="120">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="130">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="118">
         <v>-9.13</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="126">
         <v>-10</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="122">
         <v>-9.71</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="127">
         <v>-8.84</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="123">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="122">
-        <v>-11.74</v>
+      <c r="T11" s="124">
+        <v>-11.45</v>
       </c>
     </row>
     <row r="12">
@@ -5654,7 +5670,7 @@
       <c r="C12" t="str">
         <v>603966</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 1229.54万</v>
       </c>
       <c r="E12">
@@ -5669,41 +5685,41 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="132">
         <v>0</v>
       </c>
-      <c r="J12" s="137">
+      <c r="J12" s="134">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="137">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="133">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="141">
         <v>-11.82</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="138">
         <v>-15.09</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="135">
         <v>-16.1</v>
       </c>
       <c r="P12" s="142">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="143">
         <v>-16.17</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="136">
         <v>-14.77</v>
       </c>
       <c r="S12" s="131">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="140">
-        <v>9.8</v>
+      <c r="T12" s="139">
+        <v>10.19</v>
       </c>
     </row>
     <row r="13">
@@ -5716,7 +5732,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="154" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5731,41 +5747,41 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="154">
+      <c r="I13" s="155">
         <v>13.73</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="149">
         <v>2.32</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="156">
         <v>0.87</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="144">
         <v>5.22</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="150">
         <v>-1.26</v>
       </c>
-      <c r="N13" s="153">
+      <c r="N13" s="145">
         <v>-7.06</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="152">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="146">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="151">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="147">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="148">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="149">
-        <v>-18.18</v>
+      <c r="T13" s="153">
+        <v>-19.15</v>
       </c>
     </row>
     <row r="14">
@@ -5778,7 +5794,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="157" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5793,41 +5809,41 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="166">
         <v>1.04</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="163">
         <v>0.19</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="158">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="162">
+      <c r="L14" s="159">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="163">
+      <c r="M14" s="160">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="164">
         <v>-9.74</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="161">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="167">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="162">
         <v>4.35</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="168">
         <v>14.74</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="169">
         <v>11.15</v>
       </c>
-      <c r="T14" s="167">
-        <v>98.77</v>
+      <c r="T14" s="165">
+        <v>93.57</v>
       </c>
     </row>
     <row r="15">
@@ -5840,7 +5856,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5855,41 +5871,41 @@
       <c r="H15">
         <v>-2.72</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="178">
         <v>7.54</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="179">
         <v>-3.18</v>
       </c>
-      <c r="K15" s="180">
+      <c r="K15" s="173">
         <v>-0.19</v>
       </c>
       <c r="L15" s="170">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="174">
         <v>0.32</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="171">
         <v>1.56</v>
       </c>
-      <c r="O15" s="176">
+      <c r="O15" s="180">
         <v>11.7</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="181">
         <v>15.01</v>
       </c>
-      <c r="Q15" s="177">
+      <c r="Q15" s="172">
         <v>12.02</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="182">
         <v>3.18</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="175">
         <v>0.06</v>
       </c>
-      <c r="T15" s="174">
-        <v>1.3</v>
+      <c r="T15" s="176">
+        <v>2.08</v>
       </c>
     </row>
     <row r="16">
@@ -5902,7 +5918,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -5917,41 +5933,41 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="185">
         <v>0</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="193">
         <v>6.11</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="186">
         <v>16.72</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="187">
         <v>28.39</v>
       </c>
       <c r="M16" s="194">
         <v>29.42</v>
       </c>
-      <c r="N16" s="186">
+      <c r="N16" s="191">
         <v>16.48</v>
       </c>
-      <c r="O16" s="190">
+      <c r="O16" s="195">
         <v>28.13</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="188">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="191">
+      <c r="Q16" s="183">
         <v>26.42</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="189">
         <v>18.15</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="192">
         <v>24.82</v>
       </c>
-      <c r="T16" s="187">
-        <v>441.72</v>
+      <c r="T16" s="184">
+        <v>436.91</v>
       </c>
     </row>
     <row r="17">
@@ -5964,7 +5980,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="202" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -5979,41 +5995,41 @@
       <c r="H17">
         <v>-0.61</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="203">
         <v>-1.22</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="204">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="198">
         <v>-16.16</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="205">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="202">
+      <c r="M17" s="199">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="200">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="204">
+      <c r="O17" s="201">
         <v>-30.18</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="197">
         <v>-27.13</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="206">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="207">
         <v>-25.3</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="208">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="207">
-        <v>-26.52</v>
+      <c r="T17" s="196">
+        <v>-26.83</v>
       </c>
     </row>
     <row r="18">
@@ -6026,7 +6042,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="209" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6041,41 +6057,41 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="220">
+      <c r="I18" s="213">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="211">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="217">
+      <c r="K18" s="214">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="219">
         <v>-15.5</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="215">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="216">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="220">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="217">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="209">
+      <c r="Q18" s="221">
         <v>-2.95</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="218">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="219">
+      <c r="S18" s="212">
         <v>-2.58</v>
       </c>
-      <c r="T18" s="213">
-        <v>-11.07</v>
+      <c r="T18" s="210">
+        <v>-11.44</v>
       </c>
     </row>
     <row r="19">
@@ -6088,7 +6104,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="232" t="str">
+      <c r="D19" s="231" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6103,41 +6119,41 @@
       <c r="H19">
         <v>-7.17</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="232">
         <v>-3.06</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="230">
         <v>0.83</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="226">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="229">
         <v>-7.94</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="233">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="227">
         <v>-11.11</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="228">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="234">
         <v>-7.5</v>
       </c>
-      <c r="Q19" s="229">
+      <c r="Q19" s="222">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="223">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="224">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="231">
-        <v>-10.17</v>
+      <c r="T19" s="225">
+        <v>-9.28</v>
       </c>
     </row>
     <row r="20">
@@ -6150,7 +6166,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="242" t="str">
+      <c r="D20" s="235" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6165,41 +6181,41 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="236">
         <v>0</v>
       </c>
-      <c r="J20" s="236">
+      <c r="J20" s="237">
         <v>9.85</v>
       </c>
-      <c r="K20" s="243">
+      <c r="K20" s="238">
         <v>20.8</v>
       </c>
-      <c r="L20" s="240">
+      <c r="L20" s="241">
         <v>25.55</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="244">
         <v>14.23</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="239">
         <v>2.92</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="246">
         <v>-7.3</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="247">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="242">
         <v>-12.77</v>
       </c>
-      <c r="R20" s="241">
+      <c r="R20" s="245">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="240">
         <v>-12.41</v>
       </c>
-      <c r="T20" s="245">
-        <v>-50.73</v>
+      <c r="T20" s="243">
+        <v>-51.82</v>
       </c>
     </row>
     <row r="21">
@@ -6212,7 +6228,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="254" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6227,41 +6243,41 @@
       <c r="H21">
         <v>10.01</v>
       </c>
-      <c r="I21" s="253">
+      <c r="I21" s="260">
         <v>0</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="255">
         <v>10</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="259">
         <v>21</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="248">
         <v>8.91</v>
       </c>
-      <c r="M21" s="254">
+      <c r="M21" s="256">
         <v>-1.99</v>
       </c>
-      <c r="N21" s="258">
+      <c r="N21" s="251">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="255">
+      <c r="O21" s="249">
         <v>-3.41</v>
       </c>
       <c r="P21" s="250">
         <v>-10.42</v>
       </c>
-      <c r="Q21" s="259">
+      <c r="Q21" s="252">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="253">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="251">
+      <c r="S21" s="257">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="256">
-        <v>-15.21</v>
+      <c r="T21" s="258">
+        <v>-14.02</v>
       </c>
     </row>
     <row r="22">
@@ -6274,7 +6290,7 @@
       <c r="C22" t="str">
         <v>603950</v>
       </c>
-      <c r="D22" s="261" t="str">
+      <c r="D22" s="262" t="str">
         <v>净买: 6471.95万</v>
       </c>
       <c r="E22">
@@ -6289,27 +6305,29 @@
       <c r="H22">
         <v>5.99</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="263">
         <v>3.78</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="264">
         <v>6.92</v>
       </c>
-      <c r="K22" s="264">
+      <c r="K22" s="265">
         <v>13.09</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="266">
         <v>6.1</v>
       </c>
-      <c r="M22" t="str"/>
+      <c r="M22" s="267">
+        <v>2.67</v>
+      </c>
       <c r="N22" t="str"/>
       <c r="O22" t="str"/>
       <c r="P22" t="str"/>
       <c r="Q22" t="str"/>
       <c r="R22" t="str"/>
       <c r="S22" t="str"/>
-      <c r="T22" s="266">
-        <v>6.1</v>
+      <c r="T22" s="261">
+        <v>2.67</v>
       </c>
     </row>
     <row r="23">
@@ -6336,7 +6354,7 @@
         <v>21</v>
       </c>
       <c r="M23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N23">
         <v>20</v>
@@ -6371,40 +6389,40 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="267">
+      <c r="I24" s="272">
         <v>38.1</v>
       </c>
-      <c r="J24" s="278">
+      <c r="J24" s="277">
         <v>61.9</v>
       </c>
-      <c r="K24" s="271">
+      <c r="K24" s="269">
         <v>42.86</v>
       </c>
-      <c r="L24" s="268">
+      <c r="L24" s="278">
         <v>42.86</v>
       </c>
-      <c r="M24" s="272">
+      <c r="M24" s="273">
+        <v>33.33</v>
+      </c>
+      <c r="N24" s="274">
         <v>30</v>
       </c>
-      <c r="N24" s="273">
+      <c r="O24" s="270">
+        <v>25</v>
+      </c>
+      <c r="P24" s="275">
         <v>30</v>
       </c>
-      <c r="O24" s="274">
-        <v>25</v>
-      </c>
-      <c r="P24" s="269">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="275">
+      <c r="Q24" s="271">
         <v>30</v>
       </c>
       <c r="R24" s="276">
         <v>30</v>
       </c>
-      <c r="S24" s="277">
+      <c r="S24" s="279">
         <v>35</v>
       </c>
-      <c r="T24" s="270">
+      <c r="T24" s="268">
         <v>52.38</v>
       </c>
     </row>
@@ -6419,41 +6437,41 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="287">
+      <c r="I25" s="281">
         <v>2.3</v>
       </c>
-      <c r="J25" s="288">
+      <c r="J25" s="289">
         <v>0.89</v>
       </c>
       <c r="K25" s="282">
         <v>0.11</v>
       </c>
-      <c r="L25" s="289">
+      <c r="L25" s="285">
         <v>-0.09</v>
       </c>
-      <c r="M25" s="285">
-        <v>-1.6</v>
-      </c>
-      <c r="N25" s="290">
+      <c r="M25" s="288">
+        <v>-1.4</v>
+      </c>
+      <c r="N25" s="286">
         <v>-3.91</v>
       </c>
       <c r="O25" s="283">
         <v>-3.03</v>
       </c>
-      <c r="P25" s="280">
+      <c r="P25" s="290">
         <v>-1</v>
       </c>
-      <c r="Q25" s="281">
+      <c r="Q25" s="291">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="286">
+      <c r="R25" s="284">
         <v>0.57</v>
       </c>
-      <c r="S25" s="284">
+      <c r="S25" s="287">
         <v>1.47</v>
       </c>
-      <c r="T25" s="279">
-        <v>24.51</v>
+      <c r="T25" s="280">
+        <v>23.64</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="293">
+  <fills count="296">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -45,6 +45,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
@@ -63,43 +117,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,18 +303,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -135,6 +327,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -147,24 +381,618 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -177,37 +1005,481 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,13 +1491,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,25 +1539,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,7 +1557,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,529 +1623,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -819,847 +1791,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB9E2C2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1669,122 +1801,29 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="292">
+  <borders count="295">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3833,7 +3872,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="295">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4706,6 +4745,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="291" fillId="292" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="292" fillId="293" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="293" fillId="294" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="294" fillId="295" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5050,7 +5098,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="10" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5065,41 +5113,41 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="11">
         <v>7.05</v>
       </c>
       <c r="J2" s="6">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="12">
         <v>-12.87</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="13">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="1">
         <v>-27.1</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="3">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="4">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="7">
         <v>-29.13</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="8">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="9">
         <v>-38.48</v>
       </c>
       <c r="T2" s="5">
-        <v>-21.95</v>
+        <v>-23.98</v>
       </c>
     </row>
     <row r="3">
@@ -5112,7 +5160,7 @@
       <c r="C3" t="str">
         <v>601086</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 1112.14万</v>
       </c>
       <c r="E3">
@@ -5127,41 +5175,41 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="20">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="24">
         <v>10.07</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="25">
         <v>21.01</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="16">
         <v>33.16</v>
       </c>
       <c r="M3" s="21">
         <v>46.53</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="17">
         <v>61.11</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="18">
         <v>51.39</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="19">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="22">
         <v>83.16</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="14">
         <v>101.56</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="23">
         <v>121.7</v>
       </c>
-      <c r="T3" s="20">
-        <v>52.26</v>
+      <c r="T3" s="15">
+        <v>40.63</v>
       </c>
     </row>
     <row r="4">
@@ -5174,7 +5222,7 @@
       <c r="C4" t="str">
         <v>601798</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 691.01万</v>
       </c>
       <c r="E4">
@@ -5189,41 +5237,41 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="38">
         <v>0</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="29">
         <v>2.79</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="34">
         <v>-5.03</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="39">
         <v>-4.19</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="36">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="27">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="30">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="31">
         <v>-4.89</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="28">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="32">
         <v>-2.09</v>
       </c>
       <c r="S4" s="37">
         <v>2.09</v>
       </c>
       <c r="T4" s="33">
-        <v>28.07</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="5">
@@ -5236,7 +5284,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5251,41 +5299,41 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="49">
         <v>15.75</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="46">
         <v>7.62</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="50">
         <v>10.11</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="47">
         <v>21.1</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="48">
         <v>20.88</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="40">
         <v>8.79</v>
       </c>
       <c r="O5" s="41">
         <v>19.71</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="45">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="42">
         <v>44.84</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="51">
         <v>53.85</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="43">
         <v>38.46</v>
       </c>
-      <c r="T5" s="47">
-        <v>4.47</v>
+      <c r="T5" s="52">
+        <v>5.42</v>
       </c>
     </row>
     <row r="6">
@@ -5298,7 +5346,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5313,19 +5361,19 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="58">
         <v>0</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="63">
         <v>1.99</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="64">
         <v>-8.15</v>
       </c>
       <c r="L6" s="59">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="65">
         <v>-12.52</v>
       </c>
       <c r="N6" s="60">
@@ -5334,20 +5382,20 @@
       <c r="O6" s="61">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="53">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="54">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="55">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="62">
         <v>-6.96</v>
       </c>
-      <c r="T6" s="58">
-        <v>12.33</v>
+      <c r="T6" s="57">
+        <v>16.1</v>
       </c>
     </row>
     <row r="7">
@@ -5360,7 +5408,7 @@
       <c r="C7" t="str">
         <v>603280</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1485.07万</v>
       </c>
       <c r="E7">
@@ -5375,41 +5423,41 @@
       <c r="H7">
         <v>1.66</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="77">
         <v>8.18</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="78">
         <v>4.83</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="75">
         <v>0.58</v>
       </c>
       <c r="L7" s="68">
         <v>1.75</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="69">
         <v>2.46</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="74">
         <v>1.01</v>
       </c>
       <c r="O7" s="70">
         <v>0.47</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="76">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="66">
         <v>2.53</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="71">
         <v>0.19</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="72">
         <v>0.62</v>
       </c>
-      <c r="T7" s="74">
-        <v>36.13</v>
+      <c r="T7" s="67">
+        <v>32.19</v>
       </c>
     </row>
     <row r="8">
@@ -5422,7 +5470,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="88" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5437,41 +5485,41 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="91">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="89">
         <v>-6.15</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="79">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="80">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="85">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="81">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="82">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="83">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="86">
         <v>-6.51</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="87">
         <v>-6.11</v>
       </c>
       <c r="S8" s="90">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="91">
-        <v>27.02</v>
+      <c r="T8" s="84">
+        <v>23.35</v>
       </c>
     </row>
     <row r="9">
@@ -5484,7 +5532,7 @@
       <c r="C9" t="str">
         <v>600148</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -235.34万</v>
       </c>
       <c r="E9">
@@ -5499,41 +5547,41 @@
       <c r="H9">
         <v>4.88</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="104">
         <v>4.9</v>
       </c>
       <c r="J9" s="96">
         <v>3.27</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="101">
         <v>0.21</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="102">
         <v>2.76</v>
       </c>
-      <c r="M9" s="102">
+      <c r="M9" s="98">
         <v>-7.5</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="99">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="92">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="100">
         <v>-9.17</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="93">
         <v>-9.05</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="94">
         <v>-9.89</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="95">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="101">
-        <v>-23.71</v>
+      <c r="T9" s="97">
+        <v>-25.05</v>
       </c>
     </row>
     <row r="10">
@@ -5546,7 +5594,7 @@
       <c r="C10" t="str">
         <v>600620</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 848.83万</v>
       </c>
       <c r="E10">
@@ -5561,31 +5609,31 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="111">
+      <c r="I10" s="114">
         <v>0</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="111">
         <v>-10</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="110">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="106">
         <v>-15</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="115">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="107">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="108">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="109">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="112">
         <v>-18.29</v>
       </c>
       <c r="R10" s="116">
@@ -5594,8 +5642,8 @@
       <c r="S10" s="117">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="109">
-        <v>-19.61</v>
+      <c r="T10" s="113">
+        <v>-20.79</v>
       </c>
     </row>
     <row r="11">
@@ -5608,7 +5656,7 @@
       <c r="C11" t="str">
         <v>600620</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="120" t="str">
         <v>净卖: -737.07万</v>
       </c>
       <c r="E11">
@@ -5623,41 +5671,41 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="121">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="118">
         <v>-5.51</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="122">
         <v>-6.38</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="127">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="123">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="130">
+      <c r="N11" s="124">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="129">
         <v>-9.13</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="125">
         <v>-10</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="126">
         <v>-9.71</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="130">
         <v>-8.84</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="128">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="124">
-        <v>-11.45</v>
+      <c r="T11" s="119">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="12">
@@ -5685,41 +5733,41 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="137">
         <v>0</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="141">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="138">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="142">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="131">
         <v>-11.82</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="132">
         <v>-15.09</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="139">
         <v>-16.1</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="133">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="135">
         <v>-16.17</v>
       </c>
       <c r="R12" s="136">
         <v>-14.77</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="143">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="139">
-        <v>10.19</v>
+      <c r="T12" s="134">
+        <v>7.54</v>
       </c>
     </row>
     <row r="13">
@@ -5732,7 +5780,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="145" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5747,41 +5795,41 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="155">
+      <c r="I13" s="146">
         <v>13.73</v>
       </c>
-      <c r="J13" s="149">
+      <c r="J13" s="154">
         <v>2.32</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="155">
         <v>0.87</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="151">
         <v>5.22</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="147">
         <v>-1.26</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="152">
         <v>-7.06</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="153">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="148">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="156">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="144">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="149">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="153">
-        <v>-19.15</v>
+      <c r="T13" s="150">
+        <v>-21.76</v>
       </c>
     </row>
     <row r="14">
@@ -5794,7 +5842,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="157" t="str">
+      <c r="D14" s="169" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5809,41 +5857,41 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="157">
         <v>1.04</v>
       </c>
       <c r="J14" s="163">
         <v>0.19</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="162">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="158">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="164">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="165">
         <v>-9.74</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="159">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="166">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="167">
         <v>4.35</v>
       </c>
-      <c r="R14" s="168">
+      <c r="R14" s="160">
         <v>14.74</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="161">
         <v>11.15</v>
       </c>
-      <c r="T14" s="165">
-        <v>93.57</v>
+      <c r="T14" s="168">
+        <v>88.75</v>
       </c>
     </row>
     <row r="15">
@@ -5856,7 +5904,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="171" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5871,41 +5919,41 @@
       <c r="H15">
         <v>-2.72</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="181">
         <v>7.54</v>
       </c>
       <c r="J15" s="179">
         <v>-3.18</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="172">
         <v>-0.19</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="180">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="182">
         <v>0.32</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="175">
         <v>1.56</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="170">
         <v>11.7</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="173">
         <v>15.01</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="176">
         <v>12.02</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="177">
         <v>3.18</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="174">
         <v>0.06</v>
       </c>
-      <c r="T15" s="176">
-        <v>2.08</v>
+      <c r="T15" s="178">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="16">
@@ -5918,7 +5966,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -5933,41 +5981,41 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="195">
         <v>0</v>
       </c>
-      <c r="J16" s="193">
+      <c r="J16" s="188">
         <v>6.11</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="191">
         <v>16.72</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="183">
         <v>28.39</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="186">
         <v>29.42</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="189">
         <v>16.48</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="187">
         <v>28.13</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="192">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="183">
+      <c r="Q16" s="184">
         <v>26.42</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="190">
         <v>18.15</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="193">
         <v>24.82</v>
       </c>
-      <c r="T16" s="184">
-        <v>436.91</v>
+      <c r="T16" s="194">
+        <v>418.02</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +6028,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="206" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -5995,41 +6043,41 @@
       <c r="H17">
         <v>-0.61</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="207">
         <v>-1.22</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="208">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="196">
         <v>-16.16</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="197">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="198">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="199">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="200">
         <v>-30.18</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="202">
         <v>-27.13</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="203">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="207">
+      <c r="R17" s="201">
         <v>-25.3</v>
       </c>
-      <c r="S17" s="208">
+      <c r="S17" s="204">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="196">
-        <v>-26.83</v>
+      <c r="T17" s="205">
+        <v>-28.35</v>
       </c>
     </row>
     <row r="18">
@@ -6042,7 +6090,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="214" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6057,41 +6105,41 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="221">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="209">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="214">
+      <c r="K18" s="217">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="219">
+      <c r="L18" s="210">
         <v>-15.5</v>
       </c>
       <c r="M18" s="215">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="216">
+      <c r="N18" s="212">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="218">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="216">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="211">
         <v>-2.95</v>
       </c>
-      <c r="R18" s="218">
+      <c r="R18" s="219">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="213">
         <v>-2.58</v>
       </c>
-      <c r="T18" s="210">
-        <v>-11.44</v>
+      <c r="T18" s="220">
+        <v>-13.28</v>
       </c>
     </row>
     <row r="19">
@@ -6104,7 +6152,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="223" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6119,41 +6167,41 @@
       <c r="H19">
         <v>-7.17</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="229">
         <v>-3.06</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="234">
         <v>0.83</v>
       </c>
-      <c r="K19" s="226">
+      <c r="K19" s="224">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="225">
         <v>-7.94</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="222">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="226">
         <v>-11.11</v>
       </c>
-      <c r="O19" s="228">
+      <c r="O19" s="231">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="234">
+      <c r="P19" s="227">
         <v>-7.5</v>
       </c>
-      <c r="Q19" s="222">
+      <c r="Q19" s="232">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="233">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="224">
+      <c r="S19" s="228">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="225">
-        <v>-9.28</v>
+      <c r="T19" s="230">
+        <v>-8.94</v>
       </c>
     </row>
     <row r="20">
@@ -6166,7 +6214,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6181,7 +6229,7 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="242">
         <v>0</v>
       </c>
       <c r="J20" s="237">
@@ -6190,32 +6238,32 @@
       <c r="K20" s="238">
         <v>20.8</v>
       </c>
-      <c r="L20" s="241">
+      <c r="L20" s="239">
         <v>25.55</v>
       </c>
-      <c r="M20" s="244">
+      <c r="M20" s="235">
         <v>14.23</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="243">
         <v>2.92</v>
       </c>
-      <c r="O20" s="246">
+      <c r="O20" s="240">
         <v>-7.3</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="241">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="245">
         <v>-12.77</v>
       </c>
-      <c r="R20" s="245">
+      <c r="R20" s="246">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="244">
         <v>-12.41</v>
       </c>
-      <c r="T20" s="243">
-        <v>-51.82</v>
+      <c r="T20" s="236">
+        <v>-54.01</v>
       </c>
     </row>
     <row r="21">
@@ -6228,7 +6276,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6243,41 +6291,41 @@
       <c r="H21">
         <v>10.01</v>
       </c>
-      <c r="I21" s="260">
+      <c r="I21" s="254">
         <v>0</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="250">
         <v>10</v>
       </c>
-      <c r="K21" s="259">
+      <c r="K21" s="251">
         <v>21</v>
       </c>
-      <c r="L21" s="248">
+      <c r="L21" s="252">
         <v>8.91</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="255">
         <v>-1.99</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="249">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="249">
+      <c r="O21" s="256">
         <v>-3.41</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="259">
         <v>-10.42</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="257">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="260">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="258">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="258">
-        <v>-14.02</v>
+      <c r="T21" s="248">
+        <v>-14.92</v>
       </c>
     </row>
     <row r="22">
@@ -6290,7 +6338,7 @@
       <c r="C22" t="str">
         <v>603950</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="267" t="str">
         <v>净买: 6471.95万</v>
       </c>
       <c r="E22">
@@ -6305,29 +6353,35 @@
       <c r="H22">
         <v>5.99</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="262">
         <v>3.78</v>
       </c>
-      <c r="J22" s="264">
+      <c r="J22" s="268">
         <v>6.92</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="264">
         <v>13.09</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="261">
         <v>6.1</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="269">
         <v>2.67</v>
       </c>
-      <c r="N22" t="str"/>
-      <c r="O22" t="str"/>
-      <c r="P22" t="str"/>
+      <c r="N22" s="263">
+        <v>10.08</v>
+      </c>
+      <c r="O22" s="270">
+        <v>10.67</v>
+      </c>
+      <c r="P22" s="265">
+        <v>6.45</v>
+      </c>
       <c r="Q22" t="str"/>
       <c r="R22" t="str"/>
       <c r="S22" t="str"/>
-      <c r="T22" s="261">
-        <v>2.67</v>
+      <c r="T22" s="266">
+        <v>6.45</v>
       </c>
     </row>
     <row r="23">
@@ -6357,13 +6411,13 @@
         <v>21</v>
       </c>
       <c r="N23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q23">
         <v>20</v>
@@ -6389,41 +6443,41 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="272">
+      <c r="I24" s="278">
         <v>38.1</v>
       </c>
-      <c r="J24" s="277">
+      <c r="J24" s="272">
         <v>61.9</v>
       </c>
-      <c r="K24" s="269">
+      <c r="K24" s="273">
         <v>42.86</v>
       </c>
-      <c r="L24" s="278">
+      <c r="L24" s="282">
         <v>42.86</v>
       </c>
-      <c r="M24" s="273">
+      <c r="M24" s="274">
         <v>33.33</v>
       </c>
-      <c r="N24" s="274">
-        <v>30</v>
-      </c>
-      <c r="O24" s="270">
-        <v>25</v>
-      </c>
-      <c r="P24" s="275">
-        <v>30</v>
+      <c r="N24" s="281">
+        <v>33.33</v>
+      </c>
+      <c r="O24" s="275">
+        <v>28.57</v>
+      </c>
+      <c r="P24" s="276">
+        <v>33.33</v>
       </c>
       <c r="Q24" s="271">
         <v>30</v>
       </c>
-      <c r="R24" s="276">
+      <c r="R24" s="279">
         <v>30</v>
       </c>
-      <c r="S24" s="279">
+      <c r="S24" s="277">
         <v>35</v>
       </c>
-      <c r="T24" s="268">
-        <v>52.38</v>
+      <c r="T24" s="280">
+        <v>47.62</v>
       </c>
     </row>
     <row r="25">
@@ -6437,41 +6491,41 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="281">
+      <c r="I25" s="290">
         <v>2.3</v>
       </c>
-      <c r="J25" s="289">
+      <c r="J25" s="291">
         <v>0.89</v>
       </c>
-      <c r="K25" s="282">
+      <c r="K25" s="283">
         <v>0.11</v>
       </c>
       <c r="L25" s="285">
         <v>-0.09</v>
       </c>
-      <c r="M25" s="288">
+      <c r="M25" s="286">
         <v>-1.4</v>
       </c>
-      <c r="N25" s="286">
-        <v>-3.91</v>
-      </c>
-      <c r="O25" s="283">
-        <v>-3.03</v>
-      </c>
-      <c r="P25" s="290">
-        <v>-1</v>
-      </c>
-      <c r="Q25" s="291">
+      <c r="N25" s="292">
+        <v>-3.24</v>
+      </c>
+      <c r="O25" s="294">
+        <v>-2.38</v>
+      </c>
+      <c r="P25" s="293">
+        <v>-0.65</v>
+      </c>
+      <c r="Q25" s="287">
         <v>-0.19</v>
       </c>
       <c r="R25" s="284">
         <v>0.57</v>
       </c>
-      <c r="S25" s="287">
+      <c r="S25" s="288">
         <v>1.47</v>
       </c>
-      <c r="T25" s="280">
-        <v>23.64</v>
+      <c r="T25" s="289">
+        <v>20.54</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="296">
+  <fills count="297">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,36 +39,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF61BE76"/>
         <bgColor/>
       </patternFill>
@@ -93,30 +63,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -153,18 +153,126 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -177,55 +285,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,25 +459,253 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF27A644"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,13 +717,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,31 +879,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,6 +1095,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -339,31 +1143,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -375,61 +1197,325 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
+        <fgColor rgb="FFEA8992"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -441,31 +1527,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -477,145 +1593,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -627,151 +1719,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -783,127 +1761,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -915,894 +1797,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDF3F4"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF5FBF6"/>
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="295">
+  <borders count="296">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3872,7 +3885,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="296">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4754,6 +4767,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="294" fillId="295" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="295" fillId="296" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5098,7 +5114,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5113,41 +5129,41 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>7.05</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="1">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="2">
         <v>-12.87</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="10">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="8">
         <v>-27.1</v>
       </c>
       <c r="N2" s="3">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="5">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="11">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="6">
         <v>-29.13</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="12">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="4">
         <v>-38.48</v>
       </c>
-      <c r="T2" s="5">
-        <v>-23.98</v>
+      <c r="T2" s="7">
+        <v>-31.57</v>
       </c>
     </row>
     <row r="3">
@@ -5160,7 +5176,7 @@
       <c r="C3" t="str">
         <v>601086</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="20" t="str">
         <v>净买: 1112.14万</v>
       </c>
       <c r="E3">
@@ -5175,41 +5191,41 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="21">
         <v>10.07</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="23">
         <v>21.01</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="24">
         <v>33.16</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="14">
         <v>46.53</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="15">
         <v>61.11</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="16">
         <v>51.39</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="17">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="18">
         <v>83.16</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="22">
         <v>101.56</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="25">
         <v>121.7</v>
       </c>
-      <c r="T3" s="15">
-        <v>40.63</v>
+      <c r="T3" s="19">
+        <v>44.79</v>
       </c>
     </row>
     <row r="4">
@@ -5222,7 +5238,7 @@
       <c r="C4" t="str">
         <v>601798</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 691.01万</v>
       </c>
       <c r="E4">
@@ -5237,41 +5253,41 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="31">
         <v>0</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="28">
         <v>2.79</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="39">
         <v>-5.03</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="29">
         <v>-4.19</v>
       </c>
       <c r="M4" s="36">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="32">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="37">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="27">
         <v>-4.89</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="33">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="34">
         <v>-2.09</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="35">
         <v>2.09</v>
       </c>
-      <c r="T4" s="33">
-        <v>18.16</v>
+      <c r="T4" s="30">
+        <v>22.21</v>
       </c>
     </row>
     <row r="5">
@@ -5284,7 +5300,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5299,41 +5315,41 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="46">
         <v>15.75</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="43">
         <v>7.62</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="44">
         <v>10.11</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="50">
         <v>21.1</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="47">
         <v>20.88</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="48">
         <v>8.79</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="51">
         <v>19.71</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="52">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="40">
         <v>44.84</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="41">
         <v>53.85</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="49">
         <v>38.46</v>
       </c>
-      <c r="T5" s="52">
-        <v>5.42</v>
+      <c r="T5" s="42">
+        <v>4.91</v>
       </c>
     </row>
     <row r="6">
@@ -5346,7 +5362,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="61" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5361,41 +5377,41 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="56">
         <v>0</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="62">
         <v>1.99</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="63">
         <v>-8.15</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="65">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="53">
         <v>-12.52</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="64">
         <v>-11.93</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="57">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="54">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="58">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="59">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="55">
         <v>-6.96</v>
       </c>
-      <c r="T6" s="57">
-        <v>16.1</v>
+      <c r="T6" s="60">
+        <v>17.3</v>
       </c>
     </row>
     <row r="7">
@@ -5408,7 +5424,7 @@
       <c r="C7" t="str">
         <v>603280</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="74" t="str">
         <v>净买: 1485.07万</v>
       </c>
       <c r="E7">
@@ -5423,41 +5439,41 @@
       <c r="H7">
         <v>1.66</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="78">
         <v>8.18</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="71">
         <v>4.83</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="66">
         <v>0.58</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="69">
         <v>1.75</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="67">
         <v>2.46</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="68">
         <v>1.01</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="72">
         <v>0.47</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="75">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="76">
         <v>2.53</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="73">
         <v>0.19</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="77">
         <v>0.62</v>
       </c>
-      <c r="T7" s="67">
-        <v>32.19</v>
+      <c r="T7" s="70">
+        <v>34.53</v>
       </c>
     </row>
     <row r="8">
@@ -5470,7 +5486,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5485,41 +5501,41 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8" s="88">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="90">
         <v>-6.15</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="91">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="84">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="89">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="80">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="81">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="85">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="82">
         <v>-6.51</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="83">
         <v>-6.11</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="86">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="84">
-        <v>23.35</v>
+      <c r="T8" s="87">
+        <v>25.53</v>
       </c>
     </row>
     <row r="9">
@@ -5532,7 +5548,7 @@
       <c r="C9" t="str">
         <v>600148</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -235.34万</v>
       </c>
       <c r="E9">
@@ -5547,41 +5563,41 @@
       <c r="H9">
         <v>4.88</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="92">
         <v>4.9</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="93">
         <v>3.27</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="94">
         <v>0.21</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="95">
         <v>2.76</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="103">
         <v>-7.5</v>
       </c>
       <c r="N9" s="99">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="100">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="101">
         <v>-9.17</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="96">
         <v>-9.05</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="102">
         <v>-9.89</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="97">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="97">
-        <v>-25.05</v>
+      <c r="T9" s="104">
+        <v>-20.4</v>
       </c>
     </row>
     <row r="10">
@@ -5609,41 +5625,41 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="113">
         <v>0</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="114">
         <v>-10</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="106">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="116">
         <v>-15</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="107">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="108">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="109">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="110">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="115">
         <v>-18.29</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="117">
         <v>-18.03</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="111">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="113">
-        <v>-20.79</v>
+      <c r="T10" s="112">
+        <v>-20</v>
       </c>
     </row>
     <row r="11">
@@ -5656,7 +5672,7 @@
       <c r="C11" t="str">
         <v>600620</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -737.07万</v>
       </c>
       <c r="E11">
@@ -5671,31 +5687,31 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="123">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="129">
         <v>-5.51</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="119">
         <v>-6.38</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="125">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="124">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="120">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="121">
         <v>-9.13</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="126">
         <v>-10</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="127">
         <v>-9.71</v>
       </c>
       <c r="R11" s="130">
@@ -5704,8 +5720,8 @@
       <c r="S11" s="128">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="119">
-        <v>-12.75</v>
+      <c r="T11" s="118">
+        <v>-11.88</v>
       </c>
     </row>
     <row r="12">
@@ -5718,7 +5734,7 @@
       <c r="C12" t="str">
         <v>603966</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="141" t="str">
         <v>净买: 1229.54万</v>
       </c>
       <c r="E12">
@@ -5733,41 +5749,41 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="142">
         <v>0</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="139">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="135">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="143">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="132">
         <v>-11.82</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="131">
         <v>-15.09</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="136">
         <v>-16.1</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="137">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="138">
         <v>-16.17</v>
       </c>
-      <c r="R12" s="136">
+      <c r="R12" s="133">
         <v>-14.77</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="134">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="134">
-        <v>7.54</v>
+      <c r="T12" s="140">
+        <v>10.11</v>
       </c>
     </row>
     <row r="13">
@@ -5780,7 +5796,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="156" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5795,7 +5811,7 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="152">
         <v>13.73</v>
       </c>
       <c r="J13" s="154">
@@ -5804,32 +5820,32 @@
       <c r="K13" s="155">
         <v>0.87</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="149">
         <v>5.22</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="144">
         <v>-1.26</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="150">
         <v>-7.06</v>
       </c>
       <c r="O13" s="153">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="151">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="156">
+      <c r="Q13" s="145">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="146">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="147">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="150">
-        <v>-21.76</v>
+      <c r="T13" s="148">
+        <v>-20.89</v>
       </c>
     </row>
     <row r="14">
@@ -5842,7 +5858,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="165" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5857,41 +5873,41 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="166">
         <v>1.04</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="167">
         <v>0.19</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="160">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="161">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="158">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="168">
         <v>-9.74</v>
       </c>
       <c r="O14" s="159">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="169">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="162">
         <v>4.35</v>
       </c>
-      <c r="R14" s="160">
+      <c r="R14" s="163">
         <v>14.74</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="157">
         <v>11.15</v>
       </c>
-      <c r="T14" s="168">
-        <v>88.75</v>
+      <c r="T14" s="164">
+        <v>90.45</v>
       </c>
     </row>
     <row r="15">
@@ -5904,7 +5920,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="174" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5919,28 +5935,28 @@
       <c r="H15">
         <v>-2.72</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="182">
         <v>7.54</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="180">
         <v>-3.18</v>
       </c>
       <c r="K15" s="172">
         <v>-0.19</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="170">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="173">
         <v>0.32</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="181">
         <v>1.56</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="171">
         <v>11.7</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="175">
         <v>15.01</v>
       </c>
       <c r="Q15" s="176">
@@ -5949,11 +5965,11 @@
       <c r="R15" s="177">
         <v>3.18</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="178">
         <v>0.06</v>
       </c>
-      <c r="T15" s="178">
-        <v>-1.36</v>
+      <c r="T15" s="179">
+        <v>1.49</v>
       </c>
     </row>
     <row r="16">
@@ -5966,7 +5982,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="193" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -5981,41 +5997,41 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="185">
         <v>0</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="194">
         <v>6.11</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="195">
         <v>16.72</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="191">
         <v>28.39</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="187">
         <v>29.42</v>
       </c>
-      <c r="N16" s="189">
+      <c r="N16" s="183">
         <v>16.48</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="188">
         <v>28.13</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="186">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="189">
         <v>26.42</v>
       </c>
       <c r="R16" s="190">
         <v>18.15</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="184">
         <v>24.82</v>
       </c>
-      <c r="T16" s="194">
-        <v>418.02</v>
+      <c r="T16" s="192">
+        <v>431.17</v>
       </c>
     </row>
     <row r="17">
@@ -6028,7 +6044,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="205" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -6043,25 +6059,25 @@
       <c r="H17">
         <v>-0.61</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="196">
         <v>-1.22</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="199">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="206">
         <v>-16.16</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="200">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="207">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="197">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="201">
         <v>-30.18</v>
       </c>
       <c r="P17" s="202">
@@ -6070,14 +6086,14 @@
       <c r="Q17" s="203">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="201">
+      <c r="R17" s="198">
         <v>-25.3</v>
       </c>
       <c r="S17" s="204">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="205">
-        <v>-28.35</v>
+      <c r="T17" s="208">
+        <v>-27.13</v>
       </c>
     </row>
     <row r="18">
@@ -6090,7 +6106,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="214" t="str">
+      <c r="D18" s="210" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6105,41 +6121,41 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="221">
+      <c r="I18" s="211">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="214">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="217">
+      <c r="K18" s="215">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="219">
         <v>-15.5</v>
       </c>
-      <c r="M18" s="215">
+      <c r="M18" s="216">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="217">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="221">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="216">
+      <c r="P18" s="220">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="218">
         <v>-2.95</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="212">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="213">
+      <c r="S18" s="209">
         <v>-2.58</v>
       </c>
-      <c r="T18" s="220">
-        <v>-13.28</v>
+      <c r="T18" s="213">
+        <v>-11.81</v>
       </c>
     </row>
     <row r="19">
@@ -6152,7 +6168,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="229" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6167,41 +6183,41 @@
       <c r="H19">
         <v>-7.17</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="234">
         <v>-3.06</v>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="222">
         <v>0.83</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="223">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="230">
         <v>-7.94</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="224">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="225">
         <v>-11.11</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="227">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="227">
+      <c r="P19" s="228">
         <v>-7.5</v>
       </c>
       <c r="Q19" s="232">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="231">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="228">
+      <c r="S19" s="226">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="230">
-        <v>-8.94</v>
+      <c r="T19" s="233">
+        <v>-9.44</v>
       </c>
     </row>
     <row r="20">
@@ -6214,7 +6230,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="244" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6229,41 +6245,41 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="242">
+      <c r="I20" s="246">
         <v>0</v>
       </c>
       <c r="J20" s="237">
         <v>9.85</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="241">
         <v>20.8</v>
       </c>
-      <c r="L20" s="239">
+      <c r="L20" s="238">
         <v>25.55</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="239">
         <v>14.23</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="247">
         <v>2.92</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="242">
         <v>-7.3</v>
       </c>
-      <c r="P20" s="241">
+      <c r="P20" s="245">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="243">
         <v>-12.77</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="235">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="240">
         <v>-12.41</v>
       </c>
       <c r="T20" s="236">
-        <v>-54.01</v>
+        <v>-54.74</v>
       </c>
     </row>
     <row r="21">
@@ -6276,7 +6292,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="259" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6291,41 +6307,41 @@
       <c r="H21">
         <v>10.01</v>
       </c>
-      <c r="I21" s="254">
+      <c r="I21" s="251">
         <v>0</v>
       </c>
-      <c r="J21" s="250">
+      <c r="J21" s="260">
         <v>10</v>
       </c>
-      <c r="K21" s="251">
+      <c r="K21" s="248">
         <v>21</v>
       </c>
-      <c r="L21" s="252">
+      <c r="L21" s="249">
         <v>8.91</v>
       </c>
-      <c r="M21" s="255">
+      <c r="M21" s="252">
         <v>-1.99</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="253">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="250">
         <v>-3.41</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="254">
         <v>-10.42</v>
       </c>
-      <c r="Q21" s="257">
+      <c r="Q21" s="256">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="260">
+      <c r="R21" s="255">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="258">
+      <c r="S21" s="257">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="248">
-        <v>-14.92</v>
+      <c r="T21" s="258">
+        <v>-15.83</v>
       </c>
     </row>
     <row r="22">
@@ -6338,7 +6354,7 @@
       <c r="C22" t="str">
         <v>603950</v>
       </c>
-      <c r="D22" s="267" t="str">
+      <c r="D22" s="264" t="str">
         <v>净买: 6471.95万</v>
       </c>
       <c r="E22">
@@ -6356,32 +6372,34 @@
       <c r="I22" s="262">
         <v>3.78</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="270">
         <v>6.92</v>
       </c>
-      <c r="K22" s="264">
+      <c r="K22" s="271">
         <v>13.09</v>
       </c>
-      <c r="L22" s="261">
+      <c r="L22" s="265">
         <v>6.1</v>
       </c>
-      <c r="M22" s="269">
+      <c r="M22" s="263">
         <v>2.67</v>
       </c>
-      <c r="N22" s="263">
+      <c r="N22" s="266">
         <v>10.08</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="269">
         <v>10.67</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="261">
         <v>6.45</v>
       </c>
-      <c r="Q22" t="str"/>
+      <c r="Q22" s="267">
+        <v>2.32</v>
+      </c>
       <c r="R22" t="str"/>
       <c r="S22" t="str"/>
-      <c r="T22" s="266">
-        <v>6.45</v>
+      <c r="T22" s="268">
+        <v>2.32</v>
       </c>
     </row>
     <row r="23">
@@ -6420,7 +6438,7 @@
         <v>21</v>
       </c>
       <c r="Q23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R23">
         <v>20</v>
@@ -6443,41 +6461,41 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="278">
+      <c r="I24" s="283">
         <v>38.1</v>
       </c>
       <c r="J24" s="272">
         <v>61.9</v>
       </c>
-      <c r="K24" s="273">
+      <c r="K24" s="275">
         <v>42.86</v>
       </c>
-      <c r="L24" s="282">
+      <c r="L24" s="276">
         <v>42.86</v>
       </c>
-      <c r="M24" s="274">
+      <c r="M24" s="277">
         <v>33.33</v>
       </c>
-      <c r="N24" s="281">
+      <c r="N24" s="279">
         <v>33.33</v>
       </c>
-      <c r="O24" s="275">
+      <c r="O24" s="278">
         <v>28.57</v>
       </c>
-      <c r="P24" s="276">
+      <c r="P24" s="273">
         <v>33.33</v>
       </c>
-      <c r="Q24" s="271">
+      <c r="Q24" s="281">
+        <v>33.33</v>
+      </c>
+      <c r="R24" s="274">
         <v>30</v>
       </c>
-      <c r="R24" s="279">
-        <v>30</v>
-      </c>
-      <c r="S24" s="277">
+      <c r="S24" s="280">
         <v>35</v>
       </c>
-      <c r="T24" s="280">
-        <v>47.62</v>
+      <c r="T24" s="282">
+        <v>52.38</v>
       </c>
     </row>
     <row r="25">
@@ -6491,41 +6509,41 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="290">
+      <c r="I25" s="285">
         <v>2.3</v>
       </c>
-      <c r="J25" s="291">
+      <c r="J25" s="289">
         <v>0.89</v>
       </c>
-      <c r="K25" s="283">
+      <c r="K25" s="294">
         <v>0.11</v>
       </c>
-      <c r="L25" s="285">
+      <c r="L25" s="295">
         <v>-0.09</v>
       </c>
       <c r="M25" s="286">
         <v>-1.4</v>
       </c>
-      <c r="N25" s="292">
+      <c r="N25" s="287">
         <v>-3.24</v>
       </c>
-      <c r="O25" s="294">
+      <c r="O25" s="284">
         <v>-2.38</v>
       </c>
-      <c r="P25" s="293">
+      <c r="P25" s="290">
         <v>-0.65</v>
       </c>
-      <c r="Q25" s="287">
-        <v>-0.19</v>
-      </c>
-      <c r="R25" s="284">
+      <c r="Q25" s="291">
+        <v>-0.07</v>
+      </c>
+      <c r="R25" s="292">
         <v>0.57</v>
       </c>
       <c r="S25" s="288">
         <v>1.47</v>
       </c>
-      <c r="T25" s="289">
-        <v>20.54</v>
+      <c r="T25" s="293">
+        <v>21.96</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖滨四季/index.xlsx
+++ b/youzi/湖滨四季/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="297">
+  <fills count="298">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF61BE76"/>
         <bgColor/>
       </patternFill>
@@ -69,19 +117,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,30 +327,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -141,12 +351,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -159,55 +477,679 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
+        <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,43 +1161,355 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF56BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,7 +1521,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,19 +1545,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,25 +1623,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,421 +1749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FFEFA5AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -759,973 +1761,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1737,7 +1791,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1753,62 +1813,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="296">
+  <borders count="297">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3885,7 +3898,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="297">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4770,6 +4783,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="295" fillId="296" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="296" fillId="297" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5114,7 +5130,7 @@
       <c r="C2" t="str">
         <v>603359</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -1902.86万</v>
       </c>
       <c r="E2">
@@ -5129,41 +5145,41 @@
       <c r="H2">
         <v>2.79</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="4">
         <v>7.05</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="9">
         <v>-3.66</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="5">
         <v>-12.87</v>
       </c>
       <c r="L2" s="10">
         <v>-21.54</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="11">
         <v>-27.1</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="1">
         <v>-24.66</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="12">
         <v>-27.51</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="7">
         <v>-27.51</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="2">
         <v>-29.13</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="13">
         <v>-36.18</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <v>-38.48</v>
       </c>
-      <c r="T2" s="7">
-        <v>-31.57</v>
+      <c r="T2" s="8">
+        <v>-38.35</v>
       </c>
     </row>
     <row r="3">
@@ -5191,41 +5207,41 @@
       <c r="H3">
         <v>9.92</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="14">
         <v>0</v>
       </c>
       <c r="J3" s="21">
         <v>10.07</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="22">
         <v>21.01</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="17">
         <v>33.16</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="18">
         <v>46.53</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="23">
         <v>61.11</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="15">
         <v>51.39</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="24">
         <v>66.49</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="16">
         <v>83.16</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="25">
         <v>101.56</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="19">
         <v>121.7</v>
       </c>
-      <c r="T3" s="19">
-        <v>44.79</v>
+      <c r="T3" s="26">
+        <v>40.97</v>
       </c>
     </row>
     <row r="4">
@@ -5253,41 +5269,41 @@
       <c r="H4">
         <v>9.98</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="39">
         <v>0</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="33">
         <v>2.79</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="29">
         <v>-5.03</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="30">
         <v>-4.19</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="34">
         <v>-1.82</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="27">
         <v>-3.91</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="31">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="35">
         <v>-4.89</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="36">
         <v>-3.77</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="28">
         <v>-2.09</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="32">
         <v>2.09</v>
       </c>
-      <c r="T4" s="30">
-        <v>22.21</v>
+      <c r="T4" s="37">
+        <v>20.81</v>
       </c>
     </row>
     <row r="5">
@@ -5300,7 +5316,7 @@
       <c r="C5" t="str">
         <v>603332</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="48" t="str">
         <v>净卖: -1417.57万</v>
       </c>
       <c r="E5">
@@ -5315,41 +5331,41 @@
       <c r="H5">
         <v>-4.94</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="52">
         <v>15.75</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="40">
         <v>7.62</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="49">
         <v>10.11</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="41">
         <v>21.1</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="50">
         <v>20.88</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="42">
         <v>8.79</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="45">
         <v>19.71</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="43">
         <v>31.65</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="44">
         <v>44.84</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="51">
         <v>53.85</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="46">
         <v>38.46</v>
       </c>
-      <c r="T5" s="42">
-        <v>4.91</v>
+      <c r="T5" s="47">
+        <v>4.18</v>
       </c>
     </row>
     <row r="6">
@@ -5362,7 +5378,7 @@
       <c r="C6" t="str">
         <v>600207</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 486.95万</v>
       </c>
       <c r="E6">
@@ -5377,41 +5393,41 @@
       <c r="H6">
         <v>10.07</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <v>0</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="58">
         <v>1.99</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="65">
         <v>-8.15</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="53">
         <v>-15.11</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="59">
         <v>-12.52</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="55">
         <v>-11.93</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="62">
         <v>-13.52</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="60">
         <v>-12.52</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="56">
         <v>-10.34</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="54">
         <v>-9.94</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="63">
         <v>-6.96</v>
       </c>
-      <c r="T6" s="60">
-        <v>17.3</v>
+      <c r="T6" s="61">
+        <v>13.52</v>
       </c>
     </row>
     <row r="7">
@@ -5424,7 +5440,7 @@
       <c r="C7" t="str">
         <v>603280</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1485.07万</v>
       </c>
       <c r="E7">
@@ -5439,41 +5455,41 @@
       <c r="H7">
         <v>1.66</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="66">
         <v>8.18</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="74">
         <v>4.83</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="68">
         <v>0.58</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="75">
         <v>1.75</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="69">
         <v>2.46</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="76">
         <v>1.01</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="70">
         <v>0.47</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="67">
         <v>1.29</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="77">
         <v>2.53</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="78">
         <v>0.19</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="71">
         <v>0.62</v>
       </c>
-      <c r="T7" s="70">
-        <v>34.53</v>
+      <c r="T7" s="72">
+        <v>32.54</v>
       </c>
     </row>
     <row r="8">
@@ -5486,7 +5502,7 @@
       <c r="C8" t="str">
         <v>603280</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="80" t="str">
         <v>净卖: -1405.53万</v>
       </c>
       <c r="E8">
@@ -5501,41 +5517,41 @@
       <c r="H8">
         <v>-0.94</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="84">
         <v>-2.18</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="89">
         <v>-6.15</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="81">
         <v>-5.05</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="82">
         <v>-4.4</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="85">
         <v>-5.75</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="83">
         <v>-6.25</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="90">
         <v>-5.49</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="91">
         <v>-4.33</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="86">
         <v>-6.51</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="87">
         <v>-6.11</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="79">
         <v>-6.33</v>
       </c>
-      <c r="T8" s="87">
-        <v>25.53</v>
+      <c r="T8" s="88">
+        <v>23.67</v>
       </c>
     </row>
     <row r="9">
@@ -5548,7 +5564,7 @@
       <c r="C9" t="str">
         <v>600148</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -235.34万</v>
       </c>
       <c r="E9">
@@ -5563,28 +5579,28 @@
       <c r="H9">
         <v>4.88</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="98">
         <v>4.9</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="103">
         <v>3.27</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="100">
         <v>0.21</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="101">
         <v>2.76</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="104">
         <v>-7.5</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="92">
         <v>-12.86</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="95">
         <v>-10.18</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="93">
         <v>-9.17</v>
       </c>
       <c r="Q9" s="96">
@@ -5596,8 +5612,8 @@
       <c r="S9" s="97">
         <v>-11.31</v>
       </c>
-      <c r="T9" s="104">
-        <v>-20.4</v>
+      <c r="T9" s="94">
+        <v>-19.94</v>
       </c>
     </row>
     <row r="10">
@@ -5625,41 +5641,41 @@
       <c r="H10">
         <v>-1.81</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="106">
         <v>0</v>
       </c>
       <c r="J10" s="114">
         <v>-10</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="111">
         <v>-14.21</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="107">
         <v>-15</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="115">
         <v>-16.05</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="112">
         <v>-15.92</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="108">
         <v>-16.58</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="116">
         <v>-17.5</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="113">
         <v>-18.29</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="109">
         <v>-18.03</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="110">
         <v>-17.24</v>
       </c>
-      <c r="T10" s="112">
-        <v>-20</v>
+      <c r="T10" s="117">
+        <v>-20.53</v>
       </c>
     </row>
     <row r="11">
@@ -5672,7 +5688,7 @@
       <c r="C11" t="str">
         <v>600620</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="130" t="str">
         <v>净卖: -737.07万</v>
       </c>
       <c r="E11">
@@ -5687,41 +5703,41 @@
       <c r="H11">
         <v>-9.21</v>
       </c>
-      <c r="I11" s="123">
+      <c r="I11" s="118">
         <v>-0.87</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="125">
         <v>-5.51</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="126">
         <v>-6.38</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="120">
         <v>-7.54</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="121">
         <v>-7.39</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="119">
         <v>-8.12</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="127">
         <v>-9.13</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="128">
         <v>-10</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="122">
         <v>-9.71</v>
       </c>
-      <c r="R11" s="130">
+      <c r="R11" s="129">
         <v>-8.84</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="123">
         <v>-8.7</v>
       </c>
-      <c r="T11" s="118">
-        <v>-11.88</v>
+      <c r="T11" s="124">
+        <v>-12.46</v>
       </c>
     </row>
     <row r="12">
@@ -5734,7 +5750,7 @@
       <c r="C12" t="str">
         <v>603966</v>
       </c>
-      <c r="D12" s="141" t="str">
+      <c r="D12" s="131" t="str">
         <v>净买: 1229.54万</v>
       </c>
       <c r="E12">
@@ -5749,41 +5765,41 @@
       <c r="H12">
         <v>10.01</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="135">
         <v>0</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="132">
         <v>-1.24</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="141">
         <v>-11.12</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="136">
         <v>-11.28</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="137">
         <v>-11.82</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="138">
         <v>-15.09</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="142">
         <v>-16.1</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="139">
         <v>-15.94</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="143">
         <v>-16.17</v>
       </c>
       <c r="R12" s="133">
         <v>-14.77</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="140">
         <v>-13.61</v>
       </c>
-      <c r="T12" s="140">
-        <v>10.11</v>
+      <c r="T12" s="134">
+        <v>8.01</v>
       </c>
     </row>
     <row r="13">
@@ -5796,7 +5812,7 @@
       <c r="C13" t="str">
         <v>002644</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="153" t="str">
         <v>净买: 1123.39万</v>
       </c>
       <c r="E13">
@@ -5811,41 +5827,41 @@
       <c r="H13">
         <v>-3.27</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="144">
         <v>13.73</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="145">
         <v>2.32</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="146">
         <v>0.87</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="154">
         <v>5.22</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="155">
         <v>-1.26</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="149">
         <v>-7.06</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="147">
         <v>-8.7</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="156">
         <v>-8.7</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="148">
         <v>-8.03</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="150">
         <v>-8.41</v>
       </c>
-      <c r="S13" s="147">
+      <c r="S13" s="151">
         <v>-8.61</v>
       </c>
-      <c r="T13" s="148">
-        <v>-20.89</v>
+      <c r="T13" s="152">
+        <v>-21.08</v>
       </c>
     </row>
     <row r="14">
@@ -5858,7 +5874,7 @@
       <c r="C14" t="str">
         <v>000070</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="169" t="str">
         <v>净卖: -2856.82万</v>
       </c>
       <c r="E14">
@@ -5873,41 +5889,41 @@
       <c r="H14">
         <v>-3.73</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="163">
         <v>1.04</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="164">
         <v>0.19</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="159">
         <v>-5.39</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="160">
         <v>-6.43</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="168">
         <v>-9.92</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="157">
         <v>-9.74</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="165">
         <v>-0.66</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="166">
         <v>9.26</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="161">
         <v>4.35</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="158">
         <v>14.74</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="162">
         <v>11.15</v>
       </c>
-      <c r="T14" s="164">
-        <v>90.45</v>
+      <c r="T14" s="167">
+        <v>81.95</v>
       </c>
     </row>
     <row r="15">
@@ -5920,7 +5936,7 @@
       <c r="C15" t="str">
         <v>002815</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="180" t="str">
         <v>净买: 3190.46万</v>
       </c>
       <c r="E15">
@@ -5935,41 +5951,41 @@
       <c r="H15">
         <v>-2.72</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="174">
         <v>7.54</v>
       </c>
-      <c r="J15" s="180">
+      <c r="J15" s="178">
         <v>-3.18</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="175">
         <v>-0.19</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="181">
         <v>-3.25</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="172">
         <v>0.32</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="176">
         <v>1.56</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="173">
         <v>11.7</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="182">
         <v>15.01</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="170">
         <v>12.02</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="171">
         <v>3.18</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="177">
         <v>0.06</v>
       </c>
       <c r="T15" s="179">
-        <v>1.49</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="16">
@@ -5982,7 +5998,7 @@
       <c r="C16" t="str">
         <v>601869</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 5071.11万</v>
       </c>
       <c r="E16">
@@ -6000,38 +6016,38 @@
       <c r="I16" s="185">
         <v>0</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="186">
         <v>6.11</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="193">
         <v>16.72</v>
       </c>
       <c r="L16" s="191">
         <v>28.39</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="194">
         <v>29.42</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="188">
         <v>16.48</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="195">
         <v>28.13</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="183">
         <v>21.01</v>
       </c>
-      <c r="Q16" s="189">
+      <c r="Q16" s="187">
         <v>26.42</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="189">
         <v>18.15</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="192">
         <v>24.82</v>
       </c>
-      <c r="T16" s="192">
-        <v>431.17</v>
+      <c r="T16" s="184">
+        <v>425.52</v>
       </c>
     </row>
     <row r="17">
@@ -6044,7 +6060,7 @@
       <c r="C17" t="str">
         <v>600322</v>
       </c>
-      <c r="D17" s="205" t="str">
+      <c r="D17" s="197" t="str">
         <v>净买: 2077.74万</v>
       </c>
       <c r="E17">
@@ -6059,41 +6075,41 @@
       <c r="H17">
         <v>-0.61</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="206">
         <v>-1.22</v>
       </c>
-      <c r="J17" s="199">
+      <c r="J17" s="203">
         <v>-10.98</v>
       </c>
-      <c r="K17" s="206">
+      <c r="K17" s="207">
         <v>-16.16</v>
       </c>
       <c r="L17" s="200">
         <v>-22.56</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="201">
         <v>-23.48</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="204">
         <v>-28.35</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="198">
         <v>-30.18</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="208">
         <v>-27.13</v>
       </c>
-      <c r="Q17" s="203">
+      <c r="Q17" s="202">
         <v>-27.13</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="205">
         <v>-25.3</v>
       </c>
-      <c r="S17" s="204">
+      <c r="S17" s="196">
         <v>-17.68</v>
       </c>
-      <c r="T17" s="208">
-        <v>-27.13</v>
+      <c r="T17" s="199">
+        <v>-25.3</v>
       </c>
     </row>
     <row r="18">
@@ -6106,7 +6122,7 @@
       <c r="C18" t="str">
         <v>600322</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="220" t="str">
         <v>净卖: -1832.80万</v>
       </c>
       <c r="E18">
@@ -6121,41 +6137,41 @@
       <c r="H18">
         <v>-1.45</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="213">
         <v>-6.27</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="211">
         <v>-7.38</v>
       </c>
-      <c r="K18" s="215">
+      <c r="K18" s="218">
         <v>-13.28</v>
       </c>
-      <c r="L18" s="219">
+      <c r="L18" s="214">
         <v>-15.5</v>
       </c>
-      <c r="M18" s="216">
+      <c r="M18" s="221">
         <v>-11.81</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="209">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="210">
         <v>-9.59</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="215">
         <v>-0.37</v>
       </c>
-      <c r="Q18" s="218">
+      <c r="Q18" s="219">
         <v>-2.95</v>
       </c>
       <c r="R18" s="212">
         <v>-4.43</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="216">
         <v>-2.58</v>
       </c>
-      <c r="T18" s="213">
-        <v>-11.81</v>
+      <c r="T18" s="217">
+        <v>-9.59</v>
       </c>
     </row>
     <row r="19">
@@ -6168,7 +6184,7 @@
       <c r="C19" t="str">
         <v>603823</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="230" t="str">
         <v>净卖: -1462.68万</v>
       </c>
       <c r="E19">
@@ -6183,41 +6199,41 @@
       <c r="H19">
         <v>-7.17</v>
       </c>
-      <c r="I19" s="234">
+      <c r="I19" s="223">
         <v>-3.06</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="224">
         <v>0.83</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="225">
         <v>-4.17</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="234">
         <v>-7.94</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="231">
         <v>-7.44</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="228">
         <v>-11.11</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="232">
         <v>-7.44</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="226">
         <v>-7.5</v>
       </c>
-      <c r="Q19" s="232">
+      <c r="Q19" s="227">
         <v>-8.83</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="222">
         <v>-11.06</v>
       </c>
-      <c r="S19" s="226">
+      <c r="S19" s="233">
         <v>-13.5</v>
       </c>
-      <c r="T19" s="233">
-        <v>-9.44</v>
+      <c r="T19" s="229">
+        <v>-9.5</v>
       </c>
     </row>
     <row r="20">
@@ -6230,7 +6246,7 @@
       <c r="C20" t="str">
         <v>600340</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 1023.94万</v>
       </c>
       <c r="E20">
@@ -6245,10 +6261,10 @@
       <c r="H20">
         <v>10.04</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="240">
         <v>0</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="235">
         <v>9.85</v>
       </c>
       <c r="K20" s="241">
@@ -6260,25 +6276,25 @@
       <c r="M20" s="239">
         <v>14.23</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="244">
         <v>2.92</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="236">
         <v>-7.3</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="242">
         <v>-8.76</v>
       </c>
-      <c r="Q20" s="243">
+      <c r="Q20" s="237">
         <v>-12.77</v>
       </c>
-      <c r="R20" s="235">
+      <c r="R20" s="245">
         <v>-10.95</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="243">
         <v>-12.41</v>
       </c>
-      <c r="T20" s="236">
+      <c r="T20" s="246">
         <v>-54.74</v>
       </c>
     </row>
@@ -6292,7 +6308,7 @@
       <c r="C21" t="str">
         <v>603533</v>
       </c>
-      <c r="D21" s="259" t="str">
+      <c r="D21" s="248" t="str">
         <v>净买: 2395.17万</v>
       </c>
       <c r="E21">
@@ -6307,41 +6323,41 @@
       <c r="H21">
         <v>10.01</v>
       </c>
-      <c r="I21" s="251">
+      <c r="I21" s="250">
         <v>0</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="251">
         <v>10</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="254">
         <v>21</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="258">
         <v>8.91</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="259">
         <v>-1.99</v>
       </c>
-      <c r="N21" s="253">
+      <c r="N21" s="260">
         <v>-3.22</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="252">
         <v>-3.41</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="249">
         <v>-10.42</v>
       </c>
-      <c r="Q21" s="256">
+      <c r="Q21" s="255">
         <v>-14.47</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="253">
         <v>-14.25</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="256">
         <v>-12.19</v>
       </c>
-      <c r="T21" s="258">
-        <v>-15.83</v>
+      <c r="T21" s="257">
+        <v>-19.17</v>
       </c>
     </row>
     <row r="22">
@@ -6354,7 +6370,7 @@
       <c r="C22" t="str">
         <v>603950</v>
       </c>
-      <c r="D22" s="264" t="str">
+      <c r="D22" s="263" t="str">
         <v>净买: 6471.95万</v>
       </c>
       <c r="E22">
@@ -6369,37 +6385,39 @@
       <c r="H22">
         <v>5.99</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="267">
         <v>3.78</v>
       </c>
-      <c r="J22" s="270">
+      <c r="J22" s="268">
         <v>6.92</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="264">
         <v>13.09</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="271">
         <v>6.1</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="272">
         <v>2.67</v>
       </c>
-      <c r="N22" s="266">
+      <c r="N22" s="269">
         <v>10.08</v>
       </c>
-      <c r="O22" s="269">
+      <c r="O22" s="265">
         <v>10.67</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="266">
         <v>6.45</v>
       </c>
-      <c r="Q22" s="267">
+      <c r="Q22" s="261">
         <v>2.32</v>
       </c>
-      <c r="R22" t="str"/>
+      <c r="R22" s="270">
+        <v>-0.52</v>
+      </c>
       <c r="S22" t="str"/>
-      <c r="T22" s="268">
-        <v>2.32</v>
+      <c r="T22" s="262">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="23">
@@ -6441,7 +6459,7 @@
         <v>21</v>
       </c>
       <c r="R23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S23">
         <v>20</v>
@@ -6461,41 +6479,41 @@
       <c r="F24" t="str"/>
       <c r="G24" t="str"/>
       <c r="H24" t="str"/>
-      <c r="I24" s="283">
+      <c r="I24" s="273">
         <v>38.1</v>
       </c>
-      <c r="J24" s="272">
+      <c r="J24" s="283">
         <v>61.9</v>
       </c>
-      <c r="K24" s="275">
+      <c r="K24" s="274">
         <v>42.86</v>
       </c>
-      <c r="L24" s="276">
+      <c r="L24" s="275">
         <v>42.86</v>
       </c>
-      <c r="M24" s="277">
+      <c r="M24" s="280">
         <v>33.33</v>
       </c>
-      <c r="N24" s="279">
+      <c r="N24" s="281">
         <v>33.33</v>
       </c>
-      <c r="O24" s="278">
+      <c r="O24" s="276">
         <v>28.57</v>
       </c>
-      <c r="P24" s="273">
+      <c r="P24" s="284">
         <v>33.33</v>
       </c>
-      <c r="Q24" s="281">
+      <c r="Q24" s="277">
         <v>33.33</v>
       </c>
-      <c r="R24" s="274">
-        <v>30</v>
-      </c>
-      <c r="S24" s="280">
+      <c r="R24" s="278">
+        <v>28.57</v>
+      </c>
+      <c r="S24" s="282">
         <v>35</v>
       </c>
-      <c r="T24" s="282">
-        <v>52.38</v>
+      <c r="T24" s="279">
+        <v>42.86</v>
       </c>
     </row>
     <row r="25">
@@ -6509,41 +6527,41 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="285">
+      <c r="I25" s="295">
         <v>2.3</v>
       </c>
-      <c r="J25" s="289">
+      <c r="J25" s="286">
         <v>0.89</v>
       </c>
-      <c r="K25" s="294">
+      <c r="K25" s="290">
         <v>0.11</v>
       </c>
-      <c r="L25" s="295">
+      <c r="L25" s="291">
         <v>-0.09</v>
       </c>
-      <c r="M25" s="286">
+      <c r="M25" s="296">
         <v>-1.4</v>
       </c>
       <c r="N25" s="287">
         <v>-3.24</v>
       </c>
-      <c r="O25" s="284">
+      <c r="O25" s="292">
         <v>-2.38</v>
       </c>
-      <c r="P25" s="290">
+      <c r="P25" s="288">
         <v>-0.65</v>
       </c>
-      <c r="Q25" s="291">
+      <c r="Q25" s="289">
         <v>-0.07</v>
       </c>
-      <c r="R25" s="292">
-        <v>0.57</v>
-      </c>
-      <c r="S25" s="288">
+      <c r="R25" s="293">
+        <v>0.52</v>
+      </c>
+      <c r="S25" s="294">
         <v>1.47</v>
       </c>
-      <c r="T25" s="293">
-        <v>21.96</v>
+      <c r="T25" s="285">
+        <v>19.92</v>
       </c>
     </row>
   </sheetData>
